--- a/research/traditional_assets/database/data/switzerland/switzerland_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_green_renewable_energy.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07082917521137813</v>
+        <v>0.0707641946155695</v>
       </c>
       <c r="C2">
-        <v>328.3996010858414</v>
+        <v>325.9295529224031</v>
       </c>
       <c r="D2">
-        <v>316.5996010858414</v>
+        <v>317.4236945936889</v>
       </c>
       <c r="E2">
-        <v>-283.0141671285847</v>
+        <v>-279.7200254572989</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.294141671285847</v>
       </c>
       <c r="G2">
         <v>11.8</v>
@@ -1451,28 +1451,28 @@
         <v>34.89375</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1656953260656781</v>
       </c>
       <c r="N2">
-        <v>34.89375</v>
+        <v>34.72805467393432</v>
       </c>
       <c r="O2">
-        <v>5.0944875</v>
+        <v>5.07029598239441</v>
       </c>
       <c r="P2">
-        <v>29.7992625</v>
+        <v>29.65775869153991</v>
       </c>
       <c r="Q2">
-        <v>37.0292625</v>
+        <v>36.88775869153991</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07082917521137813</v>
+        <v>0.07104508345007021</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533054</v>
+        <v>0.5830273314103975</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>210.5898266929319</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0707641946155695</v>
+        <v>0.07069921401976091</v>
       </c>
       <c r="C3">
-        <v>325.9295529224031</v>
+        <v>323.4638061065569</v>
       </c>
       <c r="D3">
-        <v>317.4236945936889</v>
+        <v>318.2520894491286</v>
       </c>
       <c r="E3">
-        <v>-279.7200254572989</v>
+        <v>-276.4258837860131</v>
       </c>
       <c r="F3">
-        <v>3.294141671285847</v>
+        <v>6.588283342571694</v>
       </c>
       <c r="G3">
         <v>11.8</v>
@@ -1533,28 +1533,28 @@
         <v>34.89375</v>
       </c>
       <c r="M3">
-        <v>0.1656953260656781</v>
+        <v>0.3313906521313562</v>
       </c>
       <c r="N3">
-        <v>34.72805467393432</v>
+        <v>34.56235934786864</v>
       </c>
       <c r="O3">
-        <v>5.07029598239441</v>
+        <v>5.046104464788821</v>
       </c>
       <c r="P3">
-        <v>29.65775869153991</v>
+        <v>29.51625488307982</v>
       </c>
       <c r="Q3">
-        <v>36.88775869153991</v>
+        <v>36.74625488307982</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07104508345007021</v>
+        <v>0.07126539797934786</v>
       </c>
       <c r="T3">
-        <v>0.5830273314103975</v>
+        <v>0.5881154267747772</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>210.5898266929319</v>
+        <v>105.294913346466</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07069921401976091</v>
+        <v>0.07063423342395227</v>
       </c>
       <c r="C4">
-        <v>323.4638061065569</v>
+        <v>321.0023944026799</v>
       </c>
       <c r="D4">
-        <v>318.2520894491286</v>
+        <v>319.0848194165374</v>
       </c>
       <c r="E4">
-        <v>-276.4258837860131</v>
+        <v>-273.1317421147272</v>
       </c>
       <c r="F4">
-        <v>6.588283342571694</v>
+        <v>9.88242501385754</v>
       </c>
       <c r="G4">
         <v>11.8</v>
@@ -1615,28 +1615,28 @@
         <v>34.89375</v>
       </c>
       <c r="M4">
-        <v>0.3313906521313562</v>
+        <v>0.4970859781970343</v>
       </c>
       <c r="N4">
-        <v>34.56235934786864</v>
+        <v>34.39666402180296</v>
       </c>
       <c r="O4">
-        <v>5.046104464788821</v>
+        <v>5.021912947183232</v>
       </c>
       <c r="P4">
-        <v>29.51625488307982</v>
+        <v>29.37475107461973</v>
       </c>
       <c r="Q4">
-        <v>36.74625488307982</v>
+        <v>36.60475107461973</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07126539797934786</v>
+        <v>0.07149025507623946</v>
       </c>
       <c r="T4">
-        <v>0.5881154267747772</v>
+        <v>0.5933084313219277</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>105.294913346466</v>
+        <v>70.19660889764398</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07063423342395227</v>
+        <v>0.07056925282814368</v>
       </c>
       <c r="C5">
-        <v>321.0023944026799</v>
+        <v>318.5453519294612</v>
       </c>
       <c r="D5">
-        <v>319.0848194165374</v>
+        <v>319.9219186146046</v>
       </c>
       <c r="E5">
-        <v>-273.1317421147272</v>
+        <v>-269.8376004434414</v>
       </c>
       <c r="F5">
-        <v>9.88242501385754</v>
+        <v>13.17656668514339</v>
       </c>
       <c r="G5">
         <v>11.8</v>
@@ -1697,28 +1697,28 @@
         <v>34.89375</v>
       </c>
       <c r="M5">
-        <v>0.4970859781970343</v>
+        <v>0.6627813042627124</v>
       </c>
       <c r="N5">
-        <v>34.39666402180296</v>
+        <v>34.23096869573728</v>
       </c>
       <c r="O5">
-        <v>5.021912947183232</v>
+        <v>4.997721429577643</v>
       </c>
       <c r="P5">
-        <v>29.37475107461973</v>
+        <v>29.23324726615964</v>
       </c>
       <c r="Q5">
-        <v>36.60475107461973</v>
+        <v>36.46324726615964</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07149025507623946</v>
+        <v>0.071719796695983</v>
       </c>
       <c r="T5">
-        <v>0.5933084313219277</v>
+        <v>0.5986096234638105</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>70.19660889764398</v>
+        <v>52.64745667323297</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07056925282814368</v>
+        <v>0.07050427223233506</v>
       </c>
       <c r="C6">
-        <v>318.5453519294612</v>
+        <v>316.0927131645676</v>
       </c>
       <c r="D6">
-        <v>319.9219186146046</v>
+        <v>320.7634215209968</v>
       </c>
       <c r="E6">
-        <v>-269.8376004434414</v>
+        <v>-266.5434587721555</v>
       </c>
       <c r="F6">
-        <v>13.17656668514339</v>
+        <v>16.47070835642924</v>
       </c>
       <c r="G6">
         <v>11.8</v>
@@ -1779,28 +1779,28 @@
         <v>34.89375</v>
       </c>
       <c r="M6">
-        <v>0.6627813042627124</v>
+        <v>0.8284766303283907</v>
       </c>
       <c r="N6">
-        <v>34.23096869573728</v>
+        <v>34.06527336967161</v>
       </c>
       <c r="O6">
-        <v>4.997721429577643</v>
+        <v>4.973529911972054</v>
       </c>
       <c r="P6">
-        <v>29.23324726615964</v>
+        <v>29.09174345769955</v>
       </c>
       <c r="Q6">
-        <v>36.46324726615964</v>
+        <v>36.32174345769955</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.071719796695983</v>
+        <v>0.07195417077087901</v>
       </c>
       <c r="T6">
-        <v>0.5986096234638105</v>
+        <v>0.6040224196507856</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>52.64745667323297</v>
+        <v>42.11796533858638</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07050427223233506</v>
+        <v>0.07043929163652646</v>
       </c>
       <c r="C7">
-        <v>316.0927131645676</v>
+        <v>313.6445129493721</v>
       </c>
       <c r="D7">
-        <v>320.7634215209968</v>
+        <v>321.6093629770872</v>
       </c>
       <c r="E7">
-        <v>-266.5434587721555</v>
+        <v>-263.2493171008697</v>
       </c>
       <c r="F7">
-        <v>16.47070835642924</v>
+        <v>19.76485002771508</v>
       </c>
       <c r="G7">
         <v>11.8</v>
@@ -1861,28 +1861,28 @@
         <v>34.89375</v>
       </c>
       <c r="M7">
-        <v>0.8284766303283907</v>
+        <v>0.9941719563940687</v>
       </c>
       <c r="N7">
-        <v>34.06527336967161</v>
+        <v>33.89957804360593</v>
       </c>
       <c r="O7">
-        <v>4.973529911972054</v>
+        <v>4.949338394366465</v>
       </c>
       <c r="P7">
-        <v>29.09174345769955</v>
+        <v>28.95023964923946</v>
       </c>
       <c r="Q7">
-        <v>36.32174345769955</v>
+        <v>36.18023964923947</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07195417077087901</v>
+        <v>0.07219353152821964</v>
       </c>
       <c r="T7">
-        <v>0.6040224196507856</v>
+        <v>0.6095503817140793</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>42.11796533858638</v>
+        <v>35.09830444882198</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07043929163652646</v>
+        <v>0.07037431104071784</v>
       </c>
       <c r="C8">
-        <v>313.6445129493722</v>
+        <v>311.2007864937664</v>
       </c>
       <c r="D8">
-        <v>321.6093629770872</v>
+        <v>322.4597781927673</v>
       </c>
       <c r="E8">
-        <v>-263.2493171008697</v>
+        <v>-259.9551754295838</v>
       </c>
       <c r="F8">
-        <v>19.76485002771508</v>
+        <v>23.05899169900093</v>
       </c>
       <c r="G8">
         <v>11.8</v>
@@ -1943,28 +1943,28 @@
         <v>34.89375</v>
       </c>
       <c r="M8">
-        <v>0.9941719563940685</v>
+        <v>1.159867282459747</v>
       </c>
       <c r="N8">
-        <v>33.89957804360593</v>
+        <v>33.73388271754025</v>
       </c>
       <c r="O8">
-        <v>4.949338394366465</v>
+        <v>4.925146876760876</v>
       </c>
       <c r="P8">
-        <v>28.95023964923946</v>
+        <v>28.80873584077937</v>
       </c>
       <c r="Q8">
-        <v>36.18023964923947</v>
+        <v>36.03873584077937</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07219353152821964</v>
+        <v>0.07243803982872886</v>
       </c>
       <c r="T8">
-        <v>0.6095503817140793</v>
+        <v>0.6151972246819599</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.09830444882199</v>
+        <v>30.08426095613313</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07037431104071784</v>
+        <v>0.07030933044490922</v>
       </c>
       <c r="C9">
-        <v>311.2007864937663</v>
+        <v>308.7615693810432</v>
       </c>
       <c r="D9">
-        <v>322.4597781927673</v>
+        <v>323.3147027513299</v>
       </c>
       <c r="E9">
-        <v>-259.9551754295838</v>
+        <v>-256.6610337582979</v>
       </c>
       <c r="F9">
-        <v>23.05899169900093</v>
+        <v>26.35313337028678</v>
       </c>
       <c r="G9">
         <v>11.8</v>
@@ -2025,28 +2025,28 @@
         <v>34.89375</v>
       </c>
       <c r="M9">
-        <v>1.159867282459747</v>
+        <v>1.325562608525425</v>
       </c>
       <c r="N9">
-        <v>33.73388271754025</v>
+        <v>33.56818739147457</v>
       </c>
       <c r="O9">
-        <v>4.925146876760876</v>
+        <v>4.900955359155287</v>
       </c>
       <c r="P9">
-        <v>28.80873584077937</v>
+        <v>28.66723203231929</v>
       </c>
       <c r="Q9">
-        <v>36.03873584077937</v>
+        <v>35.89723203231929</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07243803982872886</v>
+        <v>0.07268786352707525</v>
       </c>
       <c r="T9">
-        <v>0.6151972246819599</v>
+        <v>0.6209668251056639</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.08426095613313</v>
+        <v>26.32372833661649</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07030933044490922</v>
+        <v>0.07024434984910062</v>
       </c>
       <c r="C10">
-        <v>308.7615693810432</v>
+        <v>306.3268975728609</v>
       </c>
       <c r="D10">
-        <v>323.3147027513299</v>
+        <v>324.1741726144335</v>
       </c>
       <c r="E10">
-        <v>-256.6610337582979</v>
+        <v>-253.3668920870121</v>
       </c>
       <c r="F10">
-        <v>26.35313337028678</v>
+        <v>29.64727504157262</v>
       </c>
       <c r="G10">
         <v>11.8</v>
@@ -2107,28 +2107,28 @@
         <v>34.89375</v>
       </c>
       <c r="M10">
-        <v>1.325562608525425</v>
+        <v>1.491257934591103</v>
       </c>
       <c r="N10">
-        <v>33.56818739147457</v>
+        <v>33.40249206540889</v>
       </c>
       <c r="O10">
-        <v>4.900955359155287</v>
+        <v>4.876763841549698</v>
       </c>
       <c r="P10">
-        <v>28.66723203231929</v>
+        <v>28.5257282238592</v>
       </c>
       <c r="Q10">
-        <v>35.89723203231929</v>
+        <v>35.75572822385919</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07268786352707525</v>
+        <v>0.07294317785615452</v>
       </c>
       <c r="T10">
-        <v>0.6209668251056639</v>
+        <v>0.6268632299342846</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.32372833661649</v>
+        <v>23.39886963254799</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07024434984910062</v>
+        <v>0.070179369253292</v>
       </c>
       <c r="C11">
-        <v>306.3268975728609</v>
+        <v>303.8968074142862</v>
       </c>
       <c r="D11">
-        <v>324.1741726144335</v>
+        <v>325.0382241271447</v>
       </c>
       <c r="E11">
-        <v>-253.3668920870121</v>
+        <v>-250.0727504157263</v>
       </c>
       <c r="F11">
-        <v>29.64727504157262</v>
+        <v>32.94141671285847</v>
       </c>
       <c r="G11">
         <v>11.8</v>
@@ -2189,28 +2189,28 @@
         <v>34.89375</v>
       </c>
       <c r="M11">
-        <v>1.491257934591103</v>
+        <v>1.656953260656781</v>
       </c>
       <c r="N11">
-        <v>33.40249206540889</v>
+        <v>33.23679673934322</v>
       </c>
       <c r="O11">
-        <v>4.876763841549698</v>
+        <v>4.85257232394411</v>
       </c>
       <c r="P11">
-        <v>28.5257282238592</v>
+        <v>28.38422441539911</v>
       </c>
       <c r="Q11">
-        <v>35.75572822385919</v>
+        <v>35.61422441539911</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07294317785615452</v>
+        <v>0.07320416583699112</v>
       </c>
       <c r="T11">
-        <v>0.6268632299342846</v>
+        <v>0.632890665981319</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.39886963254799</v>
+        <v>21.05898266929319</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.070179369253292</v>
+        <v>0.07011438865748339</v>
       </c>
       <c r="C12">
-        <v>303.8968074142862</v>
+        <v>301.4713356389164</v>
       </c>
       <c r="D12">
-        <v>325.0382241271447</v>
+        <v>325.9068940230607</v>
       </c>
       <c r="E12">
-        <v>-250.0727504157263</v>
+        <v>-246.7786087444404</v>
       </c>
       <c r="F12">
-        <v>32.94141671285848</v>
+        <v>36.23555838414432</v>
       </c>
       <c r="G12">
         <v>11.8</v>
@@ -2271,28 +2271,28 @@
         <v>34.89375</v>
       </c>
       <c r="M12">
-        <v>1.656953260656781</v>
+        <v>1.822648586722459</v>
       </c>
       <c r="N12">
-        <v>33.23679673934321</v>
+        <v>33.07110141327754</v>
       </c>
       <c r="O12">
-        <v>4.852572323944108</v>
+        <v>4.828380806338521</v>
       </c>
       <c r="P12">
-        <v>28.3842244153991</v>
+        <v>28.24272060693902</v>
       </c>
       <c r="Q12">
-        <v>35.61422441539911</v>
+        <v>35.47272060693902</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07320416583699112</v>
+        <v>0.07347101871627347</v>
       </c>
       <c r="T12">
-        <v>0.632890665981319</v>
+        <v>0.6390535500294104</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.05898266929319</v>
+        <v>19.14452969935745</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07011438865748339</v>
+        <v>0.07004940806167478</v>
       </c>
       <c r="C13">
-        <v>301.4713356389164</v>
+        <v>299.0505193740852</v>
       </c>
       <c r="D13">
-        <v>325.9068940230607</v>
+        <v>326.7802194295154</v>
       </c>
       <c r="E13">
-        <v>-246.7786087444404</v>
+        <v>-243.4844670731546</v>
       </c>
       <c r="F13">
-        <v>36.23555838414432</v>
+        <v>39.52970005543016</v>
       </c>
       <c r="G13">
         <v>11.8</v>
@@ -2353,28 +2353,28 @@
         <v>34.89375</v>
       </c>
       <c r="M13">
-        <v>1.822648586722459</v>
+        <v>1.988343912788137</v>
       </c>
       <c r="N13">
-        <v>33.07110141327754</v>
+        <v>32.90540608721186</v>
       </c>
       <c r="O13">
-        <v>4.828380806338521</v>
+        <v>4.804189288732931</v>
       </c>
       <c r="P13">
-        <v>28.24272060693902</v>
+        <v>28.10121679847893</v>
       </c>
       <c r="Q13">
-        <v>35.47272060693902</v>
+        <v>35.33121679847893</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07347101871627347</v>
+        <v>0.07374393643372135</v>
       </c>
       <c r="T13">
-        <v>0.6390535500294104</v>
+        <v>0.6453564996240494</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.14452969935745</v>
+        <v>17.549152224411</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07004940806167478</v>
+        <v>0.06998442746586617</v>
       </c>
       <c r="C14">
-        <v>299.0505193740852</v>
+        <v>296.634396146154</v>
       </c>
       <c r="D14">
-        <v>326.7802194295154</v>
+        <v>327.65823787287</v>
       </c>
       <c r="E14">
-        <v>-243.4844670731546</v>
+        <v>-240.1903254018687</v>
       </c>
       <c r="F14">
-        <v>39.52970005543016</v>
+        <v>42.82384172671602</v>
       </c>
       <c r="G14">
         <v>11.8</v>
@@ -2435,28 +2435,28 @@
         <v>34.89375</v>
       </c>
       <c r="M14">
-        <v>1.988343912788137</v>
+        <v>2.154039238853815</v>
       </c>
       <c r="N14">
-        <v>32.90540608721186</v>
+        <v>32.73971076114618</v>
       </c>
       <c r="O14">
-        <v>4.804189288732931</v>
+        <v>4.779997771127342</v>
       </c>
       <c r="P14">
-        <v>28.10121679847893</v>
+        <v>27.95971299001884</v>
       </c>
       <c r="Q14">
-        <v>35.33121679847893</v>
+        <v>35.18971299001885</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07374393643372135</v>
+        <v>0.07402312812168525</v>
       </c>
       <c r="T14">
-        <v>0.6453564996240494</v>
+        <v>0.6518043446116686</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.549152224411</v>
+        <v>16.19921743791784</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06998442746586617</v>
+        <v>0.06991944687005755</v>
       </c>
       <c r="C15">
-        <v>296.634396146154</v>
+        <v>294.2230038858844</v>
       </c>
       <c r="D15">
-        <v>327.65823787287</v>
+        <v>328.5409872838862</v>
       </c>
       <c r="E15">
-        <v>-240.1903254018687</v>
+        <v>-236.8961837305829</v>
       </c>
       <c r="F15">
-        <v>42.82384172671602</v>
+        <v>46.11798339800187</v>
       </c>
       <c r="G15">
         <v>11.8</v>
@@ -2517,28 +2517,28 @@
         <v>34.89375</v>
       </c>
       <c r="M15">
-        <v>2.154039238853815</v>
+        <v>2.319734564919494</v>
       </c>
       <c r="N15">
-        <v>32.73971076114618</v>
+        <v>32.5740154350805</v>
       </c>
       <c r="O15">
-        <v>4.779997771127342</v>
+        <v>4.755806253521754</v>
       </c>
       <c r="P15">
-        <v>27.95971299001884</v>
+        <v>27.81820918155875</v>
       </c>
       <c r="Q15">
-        <v>35.18971299001885</v>
+        <v>35.04820918155875</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07402312812168525</v>
+        <v>0.0743088126396018</v>
       </c>
       <c r="T15">
-        <v>0.6518043446116686</v>
+        <v>0.6584021394827207</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.19921743791784</v>
+        <v>15.04213047806656</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06991944687005755</v>
+        <v>0.06985446627424895</v>
       </c>
       <c r="C16">
-        <v>294.2230038858844</v>
+        <v>291.8163809339021</v>
       </c>
       <c r="D16">
-        <v>328.5409872838862</v>
+        <v>329.4285060031898</v>
       </c>
       <c r="E16">
-        <v>-236.8961837305829</v>
+        <v>-233.602042059297</v>
       </c>
       <c r="F16">
-        <v>46.11798339800187</v>
+        <v>49.41212506928772</v>
       </c>
       <c r="G16">
         <v>11.8</v>
@@ -2599,28 +2599,28 @@
         <v>34.89375</v>
       </c>
       <c r="M16">
-        <v>2.319734564919494</v>
+        <v>2.485429890985172</v>
       </c>
       <c r="N16">
-        <v>32.5740154350805</v>
+        <v>32.40832010901482</v>
       </c>
       <c r="O16">
-        <v>4.755806253521754</v>
+        <v>4.731614735916164</v>
       </c>
       <c r="P16">
-        <v>27.81820918155875</v>
+        <v>27.67670537309866</v>
       </c>
       <c r="Q16">
-        <v>35.04820918155875</v>
+        <v>34.90670537309866</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0743088126396018</v>
+        <v>0.07460121914617523</v>
       </c>
       <c r="T16">
-        <v>0.6584021394827207</v>
+        <v>0.6651551765860331</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.04213047806656</v>
+        <v>14.03932177952879</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06985446627424895</v>
+        <v>0.06978948567844033</v>
       </c>
       <c r="C17">
-        <v>291.8163809339021</v>
+        <v>289.4145660462484</v>
       </c>
       <c r="D17">
-        <v>329.4285060031898</v>
+        <v>330.3208327868219</v>
       </c>
       <c r="E17">
-        <v>-233.602042059297</v>
+        <v>-230.3079003880112</v>
       </c>
       <c r="F17">
-        <v>49.4121250692877</v>
+        <v>52.70626674057355</v>
       </c>
       <c r="G17">
         <v>11.8</v>
@@ -2681,28 +2681,28 @@
         <v>34.89375</v>
       </c>
       <c r="M17">
-        <v>2.485429890985171</v>
+        <v>2.65112521705085</v>
       </c>
       <c r="N17">
-        <v>32.40832010901482</v>
+        <v>32.24262478294915</v>
       </c>
       <c r="O17">
-        <v>4.731614735916164</v>
+        <v>4.707423218310575</v>
       </c>
       <c r="P17">
-        <v>27.67670537309866</v>
+        <v>27.53520156463858</v>
       </c>
       <c r="Q17">
-        <v>34.90670537309866</v>
+        <v>34.76520156463857</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07460121914617523</v>
+        <v>0.07490058771242897</v>
       </c>
       <c r="T17">
-        <v>0.6651551765860331</v>
+        <v>0.6720690002870432</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.03932177952879</v>
+        <v>13.16186416830825</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06978948567844033</v>
+        <v>0.06994227508263172</v>
       </c>
       <c r="C18">
-        <v>289.4145660462484</v>
+        <v>284.0299203499375</v>
       </c>
       <c r="D18">
-        <v>330.3208327868219</v>
+        <v>328.2303287617969</v>
       </c>
       <c r="E18">
-        <v>-230.3079003880112</v>
+        <v>-227.0137587167253</v>
       </c>
       <c r="F18">
-        <v>52.70626674057355</v>
+        <v>56.0004084118594</v>
       </c>
       <c r="G18">
         <v>11.8</v>
@@ -2763,45 +2763,45 @@
         <v>34.89375</v>
       </c>
       <c r="M18">
-        <v>2.65112521705085</v>
+        <v>2.900821155734317</v>
       </c>
       <c r="N18">
-        <v>32.24262478294915</v>
+        <v>31.99292884426568</v>
       </c>
       <c r="O18">
-        <v>4.707423218310575</v>
+        <v>4.670967611262789</v>
       </c>
       <c r="P18">
-        <v>27.53520156463858</v>
+        <v>27.32196123300289</v>
       </c>
       <c r="Q18">
-        <v>34.76520156463857</v>
+        <v>34.55196123300289</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07490058771242897</v>
+        <v>0.07520716997907437</v>
       </c>
       <c r="T18">
-        <v>0.6720690002870432</v>
+        <v>0.6791494221495233</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.16186416830825</v>
+        <v>12.02892151107708</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06994227508263172</v>
+        <v>0.0698901044868231</v>
       </c>
       <c r="C19">
-        <v>284.0299203499375</v>
+        <v>281.4466087966085</v>
       </c>
       <c r="D19">
-        <v>328.2303287617969</v>
+        <v>328.9411588797537</v>
       </c>
       <c r="E19">
-        <v>-227.0137587167253</v>
+        <v>-223.7196170454395</v>
       </c>
       <c r="F19">
-        <v>56.0004084118594</v>
+        <v>59.29455008314525</v>
       </c>
       <c r="G19">
         <v>11.8</v>
@@ -2845,28 +2845,28 @@
         <v>34.89375</v>
       </c>
       <c r="M19">
-        <v>2.900821155734317</v>
+        <v>3.071457694306924</v>
       </c>
       <c r="N19">
-        <v>31.99292884426568</v>
+        <v>31.82229230569307</v>
       </c>
       <c r="O19">
-        <v>4.670967611262789</v>
+        <v>4.646054676631188</v>
       </c>
       <c r="P19">
-        <v>27.32196123300289</v>
+        <v>27.17623762906188</v>
       </c>
       <c r="Q19">
-        <v>34.55196123300289</v>
+        <v>34.40623762906188</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07520716997907437</v>
+        <v>0.0755212298619794</v>
       </c>
       <c r="T19">
-        <v>0.6791494221495233</v>
+        <v>0.6864025372281617</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.02892151107708</v>
+        <v>11.36064809379502</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06989010448682312</v>
+        <v>0.0698379338910145</v>
       </c>
       <c r="C20">
-        <v>281.4466087966083</v>
+        <v>278.8663827356465</v>
       </c>
       <c r="D20">
-        <v>328.9411588797535</v>
+        <v>329.6550744900776</v>
       </c>
       <c r="E20">
-        <v>-223.7196170454395</v>
+        <v>-220.4254753741536</v>
       </c>
       <c r="F20">
-        <v>59.29455008314525</v>
+        <v>62.5886917544311</v>
       </c>
       <c r="G20">
         <v>11.8</v>
@@ -2927,28 +2927,28 @@
         <v>34.89375</v>
       </c>
       <c r="M20">
-        <v>3.071457694306924</v>
+        <v>3.242094232879531</v>
       </c>
       <c r="N20">
-        <v>31.82229230569308</v>
+        <v>31.65165576712047</v>
       </c>
       <c r="O20">
-        <v>4.646054676631189</v>
+        <v>4.621141741999588</v>
       </c>
       <c r="P20">
-        <v>27.17623762906189</v>
+        <v>27.03051402512088</v>
       </c>
       <c r="Q20">
-        <v>34.40623762906189</v>
+        <v>34.26051402512088</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0755212298619794</v>
+        <v>0.07584304430989444</v>
       </c>
       <c r="T20">
-        <v>0.6864025372281617</v>
+        <v>0.693834741568001</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.36064809379502</v>
+        <v>10.76271924675318</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0698379338910145</v>
+        <v>0.06978576329520589</v>
       </c>
       <c r="C21">
-        <v>278.8663827356465</v>
+        <v>276.2892623004919</v>
       </c>
       <c r="D21">
-        <v>329.6550744900776</v>
+        <v>330.3720957262089</v>
       </c>
       <c r="E21">
-        <v>-220.4254753741536</v>
+        <v>-217.1313337028678</v>
       </c>
       <c r="F21">
-        <v>62.5886917544311</v>
+        <v>65.88283342571695</v>
       </c>
       <c r="G21">
         <v>11.8</v>
@@ -3009,28 +3009,28 @@
         <v>34.89375</v>
       </c>
       <c r="M21">
-        <v>3.242094232879531</v>
+        <v>3.412730771452138</v>
       </c>
       <c r="N21">
-        <v>31.65165576712047</v>
+        <v>31.48101922854786</v>
       </c>
       <c r="O21">
-        <v>4.621141741999588</v>
+        <v>4.596228807367987</v>
       </c>
       <c r="P21">
-        <v>27.03051402512088</v>
+        <v>26.88479042117987</v>
       </c>
       <c r="Q21">
-        <v>34.26051402512088</v>
+        <v>34.11479042117988</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07584304430989444</v>
+        <v>0.07617290411900736</v>
       </c>
       <c r="T21">
-        <v>0.693834741568001</v>
+        <v>0.7014527510163362</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.76271924675318</v>
+        <v>10.22458328441552</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06978576329520589</v>
+        <v>0.07003847069939727</v>
       </c>
       <c r="C22">
-        <v>276.2892623004919</v>
+        <v>269.5507005680711</v>
       </c>
       <c r="D22">
-        <v>330.3720957262089</v>
+        <v>326.9276756650739</v>
       </c>
       <c r="E22">
-        <v>-217.1313337028678</v>
+        <v>-213.8371920315819</v>
       </c>
       <c r="F22">
-        <v>65.88283342571695</v>
+        <v>69.1769750970028</v>
       </c>
       <c r="G22">
         <v>11.8</v>
@@ -3091,45 +3091,45 @@
         <v>34.89375</v>
       </c>
       <c r="M22">
-        <v>3.412730771452138</v>
+        <v>3.700968167689649</v>
       </c>
       <c r="N22">
-        <v>31.48101922854786</v>
+        <v>31.19278183231035</v>
       </c>
       <c r="O22">
-        <v>4.596228807367987</v>
+        <v>4.554146147517311</v>
       </c>
       <c r="P22">
-        <v>26.88479042117987</v>
+        <v>26.63863568479304</v>
       </c>
       <c r="Q22">
-        <v>34.11479042117988</v>
+        <v>33.86863568479303</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07617290411900736</v>
+        <v>0.07651111480936362</v>
       </c>
       <c r="T22">
-        <v>0.7014527510163362</v>
+        <v>0.7092636214633633</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.146</v>
       </c>
       <c r="W22">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.22458328441552</v>
+        <v>9.428276175037361</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07003847069939727</v>
+        <v>0.07000081810358866</v>
       </c>
       <c r="C23">
-        <v>269.5507005680711</v>
+        <v>266.7652059837463</v>
       </c>
       <c r="D23">
-        <v>326.9276756650739</v>
+        <v>327.436322752035</v>
       </c>
       <c r="E23">
-        <v>-213.8371920315819</v>
+        <v>-210.5430503602961</v>
       </c>
       <c r="F23">
-        <v>69.1769750970028</v>
+        <v>72.47111676828864</v>
       </c>
       <c r="G23">
         <v>11.8</v>
@@ -3173,28 +3173,28 @@
         <v>34.89375</v>
       </c>
       <c r="M23">
-        <v>3.700968167689649</v>
+        <v>3.877204747103442</v>
       </c>
       <c r="N23">
-        <v>31.19278183231035</v>
+        <v>31.01654525289656</v>
       </c>
       <c r="O23">
-        <v>4.554146147517311</v>
+        <v>4.528415606922897</v>
       </c>
       <c r="P23">
-        <v>26.63863568479304</v>
+        <v>26.48812964597366</v>
       </c>
       <c r="Q23">
-        <v>33.86863568479303</v>
+        <v>33.71812964597366</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07651111480936362</v>
+        <v>0.0768579975687034</v>
       </c>
       <c r="T23">
-        <v>0.7092636214633633</v>
+        <v>0.7172747706398016</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.428276175037361</v>
+        <v>8.999718167081117</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07000081810358866</v>
+        <v>0.06996316550778005</v>
       </c>
       <c r="C24">
-        <v>266.7652059837463</v>
+        <v>263.9812966125153</v>
       </c>
       <c r="D24">
-        <v>327.436322752035</v>
+        <v>327.9465550520898</v>
       </c>
       <c r="E24">
-        <v>-210.5430503602961</v>
+        <v>-207.2489086890102</v>
       </c>
       <c r="F24">
-        <v>72.47111676828864</v>
+        <v>75.7652584395745</v>
       </c>
       <c r="G24">
         <v>11.8</v>
@@ -3255,28 +3255,28 @@
         <v>34.89375</v>
       </c>
       <c r="M24">
-        <v>3.877204747103442</v>
+        <v>4.053441326517236</v>
       </c>
       <c r="N24">
-        <v>31.01654525289656</v>
+        <v>30.84030867348276</v>
       </c>
       <c r="O24">
-        <v>4.528415606922897</v>
+        <v>4.502685066328483</v>
       </c>
       <c r="P24">
-        <v>26.48812964597366</v>
+        <v>26.33762360715428</v>
       </c>
       <c r="Q24">
-        <v>33.71812964597366</v>
+        <v>33.56762360715427</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0768579975687034</v>
+        <v>0.07721389026984421</v>
       </c>
       <c r="T24">
-        <v>0.7172747706398016</v>
+        <v>0.7254940016130305</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.999718167081117</v>
+        <v>8.608426072860198</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06996316550778005</v>
+        <v>0.06992551291197144</v>
       </c>
       <c r="C25">
-        <v>263.9812966125153</v>
+        <v>261.1989798764861</v>
       </c>
       <c r="D25">
-        <v>327.9465550520898</v>
+        <v>328.4583799873464</v>
       </c>
       <c r="E25">
-        <v>-207.2489086890102</v>
+        <v>-203.9547670177244</v>
       </c>
       <c r="F25">
-        <v>75.7652584395745</v>
+        <v>79.05940011086034</v>
       </c>
       <c r="G25">
         <v>11.8</v>
@@ -3337,28 +3337,28 @@
         <v>34.89375</v>
       </c>
       <c r="M25">
-        <v>4.053441326517236</v>
+        <v>4.229677905931028</v>
       </c>
       <c r="N25">
-        <v>30.84030867348276</v>
+        <v>30.66407209406897</v>
       </c>
       <c r="O25">
-        <v>4.502685066328483</v>
+        <v>4.47695452573407</v>
       </c>
       <c r="P25">
-        <v>26.33762360715428</v>
+        <v>26.1871175683349</v>
       </c>
       <c r="Q25">
-        <v>33.56762360715427</v>
+        <v>33.4171175683349</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07721389026984421</v>
+        <v>0.07757914856838347</v>
       </c>
       <c r="T25">
-        <v>0.7254940016130305</v>
+        <v>0.7339295281381863</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.608426072860198</v>
+        <v>8.249741653157692</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06992551291197144</v>
+        <v>0.06988786031616283</v>
       </c>
       <c r="C26">
-        <v>261.1989798764861</v>
+        <v>258.4182632441738</v>
       </c>
       <c r="D26">
-        <v>328.4583799873464</v>
+        <v>328.9718050263199</v>
       </c>
       <c r="E26">
-        <v>-203.9547670177244</v>
+        <v>-200.6606253464386</v>
       </c>
       <c r="F26">
-        <v>79.05940011086032</v>
+        <v>82.35354178214618</v>
       </c>
       <c r="G26">
         <v>11.8</v>
@@ -3419,28 +3419,28 @@
         <v>34.89375</v>
       </c>
       <c r="M26">
-        <v>4.229677905931028</v>
+        <v>4.40591448534482</v>
       </c>
       <c r="N26">
-        <v>30.66407209406897</v>
+        <v>30.48783551465518</v>
       </c>
       <c r="O26">
-        <v>4.47695452573407</v>
+        <v>4.451223985139656</v>
       </c>
       <c r="P26">
-        <v>26.1871175683349</v>
+        <v>26.03661152951552</v>
       </c>
       <c r="Q26">
-        <v>33.4171175683349</v>
+        <v>33.26661152951552</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07757914856838347</v>
+        <v>0.0779541470882171</v>
       </c>
       <c r="T26">
-        <v>0.7339295281381863</v>
+        <v>0.7425900020373464</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.249741653157692</v>
+        <v>7.919751987031383</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06988786031616283</v>
+        <v>0.0698502077203542</v>
       </c>
       <c r="C27">
-        <v>258.4182632441738</v>
+        <v>255.6391542308639</v>
       </c>
       <c r="D27">
-        <v>328.9718050263199</v>
+        <v>329.4868376842959</v>
       </c>
       <c r="E27">
-        <v>-200.6606253464386</v>
+        <v>-197.3664836751527</v>
       </c>
       <c r="F27">
-        <v>82.35354178214618</v>
+        <v>85.64768345343204</v>
       </c>
       <c r="G27">
         <v>11.8</v>
@@ -3501,28 +3501,28 @@
         <v>34.89375</v>
       </c>
       <c r="M27">
-        <v>4.40591448534482</v>
+        <v>4.582151064758614</v>
       </c>
       <c r="N27">
-        <v>30.48783551465518</v>
+        <v>30.31159893524138</v>
       </c>
       <c r="O27">
-        <v>4.451223985139656</v>
+        <v>4.425493444545242</v>
       </c>
       <c r="P27">
-        <v>26.03661152951552</v>
+        <v>25.88610549069614</v>
       </c>
       <c r="Q27">
-        <v>33.26661152951552</v>
+        <v>33.11610549069614</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0779541470882171</v>
+        <v>0.07833928070318136</v>
       </c>
       <c r="T27">
-        <v>0.7425900020373464</v>
+        <v>0.7514845427986458</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.919751987031383</v>
+        <v>7.61514614137633</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0698502077203542</v>
+        <v>0.06999701912454559</v>
       </c>
       <c r="C28">
-        <v>255.6391542308639</v>
+        <v>250.3459057665458</v>
       </c>
       <c r="D28">
-        <v>329.4868376842959</v>
+        <v>327.4877308912637</v>
       </c>
       <c r="E28">
-        <v>-197.3664836751527</v>
+        <v>-194.0723420038669</v>
       </c>
       <c r="F28">
-        <v>85.64768345343204</v>
+        <v>88.94182512471788</v>
       </c>
       <c r="G28">
         <v>11.8</v>
@@ -3583,45 +3583,45 @@
         <v>34.89375</v>
       </c>
       <c r="M28">
-        <v>4.582151064758614</v>
+        <v>4.829541104272181</v>
       </c>
       <c r="N28">
-        <v>30.31159893524138</v>
+        <v>30.06420889572782</v>
       </c>
       <c r="O28">
-        <v>4.425493444545242</v>
+        <v>4.389374498776261</v>
       </c>
       <c r="P28">
-        <v>25.88610549069614</v>
+        <v>25.67483439695155</v>
       </c>
       <c r="Q28">
-        <v>33.11610549069614</v>
+        <v>32.90483439695156</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07833928070318136</v>
+        <v>0.07873496592403506</v>
       </c>
       <c r="T28">
-        <v>0.7514845427986458</v>
+        <v>0.7606227696082002</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.61514614137633</v>
+        <v>7.225065331597077</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06999701912454559</v>
+        <v>0.06996619852873698</v>
       </c>
       <c r="C29">
-        <v>250.3459057665458</v>
+        <v>247.469428750877</v>
       </c>
       <c r="D29">
-        <v>327.4877308912637</v>
+        <v>327.9053955468808</v>
       </c>
       <c r="E29">
-        <v>-194.0723420038669</v>
+        <v>-190.778200332581</v>
       </c>
       <c r="F29">
-        <v>88.94182512471788</v>
+        <v>92.23596679600374</v>
       </c>
       <c r="G29">
         <v>11.8</v>
@@ -3665,28 +3665,28 @@
         <v>34.89375</v>
       </c>
       <c r="M29">
-        <v>4.829541104272181</v>
+        <v>5.008412997023003</v>
       </c>
       <c r="N29">
-        <v>30.06420889572782</v>
+        <v>29.885337002977</v>
       </c>
       <c r="O29">
-        <v>4.389374498776261</v>
+        <v>4.363259202434641</v>
       </c>
       <c r="P29">
-        <v>25.67483439695155</v>
+        <v>25.52207780054236</v>
       </c>
       <c r="Q29">
-        <v>32.90483439695156</v>
+        <v>32.75207780054235</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07873496592403506</v>
+        <v>0.07914164240102359</v>
       </c>
       <c r="T29">
-        <v>0.7606227696082002</v>
+        <v>0.7700148360513532</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.225065331597077</v>
+        <v>6.967027284040038</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06996619852873698</v>
+        <v>0.06993537793292838</v>
       </c>
       <c r="C30">
-        <v>247.469428750877</v>
+        <v>244.594018440985</v>
       </c>
       <c r="D30">
-        <v>327.9053955468808</v>
+        <v>328.3241269082746</v>
       </c>
       <c r="E30">
-        <v>-190.778200332581</v>
+        <v>-187.4840586612952</v>
       </c>
       <c r="F30">
-        <v>92.23596679600374</v>
+        <v>95.53010846728958</v>
       </c>
       <c r="G30">
         <v>11.8</v>
@@ -3747,28 +3747,28 @@
         <v>34.89375</v>
       </c>
       <c r="M30">
-        <v>5.008412997023003</v>
+        <v>5.187284889773824</v>
       </c>
       <c r="N30">
-        <v>29.885337002977</v>
+        <v>29.70646511022617</v>
       </c>
       <c r="O30">
-        <v>4.363259202434641</v>
+        <v>4.337143906093021</v>
       </c>
       <c r="P30">
-        <v>25.52207780054236</v>
+        <v>25.36932120413315</v>
       </c>
       <c r="Q30">
-        <v>32.75207780054235</v>
+        <v>32.59932120413315</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07914164240102359</v>
+        <v>0.07955977455342025</v>
       </c>
       <c r="T30">
-        <v>0.7700148360513532</v>
+        <v>0.779671467746426</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.967027284040038</v>
+        <v>6.726784963900726</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06993537793292838</v>
+        <v>0.06990455733711977</v>
       </c>
       <c r="C31">
-        <v>244.5940184409851</v>
+        <v>241.7196789286076</v>
       </c>
       <c r="D31">
-        <v>328.3241269082746</v>
+        <v>328.743929067183</v>
       </c>
       <c r="E31">
-        <v>-187.4840586612952</v>
+        <v>-184.1899169900094</v>
       </c>
       <c r="F31">
-        <v>95.53010846728957</v>
+        <v>98.82425013857541</v>
       </c>
       <c r="G31">
         <v>11.8</v>
@@ -3829,28 +3829,28 @@
         <v>34.89375</v>
       </c>
       <c r="M31">
-        <v>5.187284889773824</v>
+        <v>5.366156782524644</v>
       </c>
       <c r="N31">
-        <v>29.70646511022617</v>
+        <v>29.52759321747535</v>
       </c>
       <c r="O31">
-        <v>4.337143906093021</v>
+        <v>4.311028609751402</v>
       </c>
       <c r="P31">
-        <v>25.36932120413315</v>
+        <v>25.21656460772395</v>
       </c>
       <c r="Q31">
-        <v>32.59932120413315</v>
+        <v>32.44656460772396</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07955977455342025</v>
+        <v>0.07998985333874252</v>
       </c>
       <c r="T31">
-        <v>0.779671467746426</v>
+        <v>0.7896040032042153</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.726784963900727</v>
+        <v>6.50255879843737</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06990455733711977</v>
+        <v>0.06987373674131116</v>
       </c>
       <c r="C32">
-        <v>241.7196789286076</v>
+        <v>238.8464143264361</v>
       </c>
       <c r="D32">
-        <v>328.743929067183</v>
+        <v>329.1648061362974</v>
       </c>
       <c r="E32">
-        <v>-184.1899169900094</v>
+        <v>-180.8957753187235</v>
       </c>
       <c r="F32">
-        <v>98.82425013857541</v>
+        <v>102.1183918098613</v>
       </c>
       <c r="G32">
         <v>11.8</v>
@@ -3911,28 +3911,28 @@
         <v>34.89375</v>
       </c>
       <c r="M32">
-        <v>5.366156782524644</v>
+        <v>5.545028675275467</v>
       </c>
       <c r="N32">
-        <v>29.52759321747535</v>
+        <v>29.34872132472453</v>
       </c>
       <c r="O32">
-        <v>4.311028609751402</v>
+        <v>4.284913313409781</v>
       </c>
       <c r="P32">
-        <v>25.21656460772395</v>
+        <v>25.06380801131475</v>
       </c>
       <c r="Q32">
-        <v>32.44656460772396</v>
+        <v>32.29380801131475</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07998985333874252</v>
+        <v>0.08043239817581327</v>
       </c>
       <c r="T32">
-        <v>0.7896040032042153</v>
+        <v>0.7998244382404912</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.50255879843737</v>
+        <v>6.292798837197454</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06987373674131116</v>
+        <v>0.07011619614550253</v>
       </c>
       <c r="C33">
-        <v>238.8464143264361</v>
+        <v>232.2701350091543</v>
       </c>
       <c r="D33">
-        <v>329.1648061362974</v>
+        <v>325.8826684903014</v>
       </c>
       <c r="E33">
-        <v>-180.8957753187235</v>
+        <v>-177.6016336474376</v>
       </c>
       <c r="F33">
-        <v>102.1183918098613</v>
+        <v>105.4125334811471</v>
       </c>
       <c r="G33">
         <v>11.8</v>
@@ -3993,45 +3993,45 @@
         <v>34.89375</v>
       </c>
       <c r="M33">
-        <v>5.545028675275467</v>
+        <v>5.829313101507435</v>
       </c>
       <c r="N33">
-        <v>29.34872132472453</v>
+        <v>29.06443689849256</v>
       </c>
       <c r="O33">
-        <v>4.284913313409781</v>
+        <v>4.243407787179914</v>
       </c>
       <c r="P33">
-        <v>25.06380801131475</v>
+        <v>24.82102911131265</v>
       </c>
       <c r="Q33">
-        <v>32.29380801131475</v>
+        <v>32.05102911131264</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08043239817581327</v>
+        <v>0.08088795903750373</v>
       </c>
       <c r="T33">
-        <v>0.7998244382404912</v>
+        <v>0.8103454743072457</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.146</v>
       </c>
       <c r="W33">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.292798837197454</v>
+        <v>5.985911100053388</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07011619614550253</v>
+        <v>0.07009391554969394</v>
       </c>
       <c r="C34">
-        <v>232.2701350091543</v>
+        <v>229.2748689967883</v>
       </c>
       <c r="D34">
-        <v>325.8826684903014</v>
+        <v>326.1815441492213</v>
       </c>
       <c r="E34">
-        <v>-177.6016336474376</v>
+        <v>-174.3074919761518</v>
       </c>
       <c r="F34">
-        <v>105.4125334811471</v>
+        <v>108.706675152433</v>
       </c>
       <c r="G34">
         <v>11.8</v>
@@ -4075,28 +4075,28 @@
         <v>34.89375</v>
       </c>
       <c r="M34">
-        <v>5.829313101507435</v>
+        <v>6.011479135929543</v>
       </c>
       <c r="N34">
-        <v>29.06443689849256</v>
+        <v>28.88227086407046</v>
       </c>
       <c r="O34">
-        <v>4.243407787179914</v>
+        <v>4.216811546154286</v>
       </c>
       <c r="P34">
-        <v>24.82102911131265</v>
+        <v>24.66545931791617</v>
       </c>
       <c r="Q34">
-        <v>32.05102911131264</v>
+        <v>31.89545931791617</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08088795903750373</v>
+        <v>0.08135711873088647</v>
       </c>
       <c r="T34">
-        <v>0.8103454743072457</v>
+        <v>0.8211805711521123</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.985911100053388</v>
+        <v>5.804519854597225</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07009391554969394</v>
+        <v>0.07007163495388531</v>
       </c>
       <c r="C35">
-        <v>229.2748689967883</v>
+        <v>226.2801517012905</v>
       </c>
       <c r="D35">
-        <v>326.1815441492213</v>
+        <v>326.4809685250093</v>
       </c>
       <c r="E35">
-        <v>-174.3074919761518</v>
+        <v>-171.0133503048659</v>
       </c>
       <c r="F35">
-        <v>108.706675152433</v>
+        <v>112.0008168237188</v>
       </c>
       <c r="G35">
         <v>11.8</v>
@@ -4157,28 +4157,28 @@
         <v>34.89375</v>
       </c>
       <c r="M35">
-        <v>6.011479135929543</v>
+        <v>6.19364517035165</v>
       </c>
       <c r="N35">
-        <v>28.88227086407046</v>
+        <v>28.70010482964835</v>
       </c>
       <c r="O35">
-        <v>4.216811546154286</v>
+        <v>4.190215305128659</v>
       </c>
       <c r="P35">
-        <v>24.66545931791617</v>
+        <v>24.50988952451969</v>
       </c>
       <c r="Q35">
-        <v>31.89545931791617</v>
+        <v>31.73988952451969</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08135711873088647</v>
+        <v>0.08184049538467472</v>
       </c>
       <c r="T35">
-        <v>0.8211805711521123</v>
+        <v>0.8323440042650052</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.804519854597225</v>
+        <v>5.633798682403188</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07007163495388531</v>
+        <v>0.07004935435807669</v>
       </c>
       <c r="C36">
-        <v>226.2801517012905</v>
+        <v>223.2859846351632</v>
       </c>
       <c r="D36">
-        <v>326.4809685250093</v>
+        <v>326.7809431301679</v>
       </c>
       <c r="E36">
-        <v>-171.0133503048659</v>
+        <v>-167.7192086335801</v>
       </c>
       <c r="F36">
-        <v>112.0008168237188</v>
+        <v>115.2949584950047</v>
       </c>
       <c r="G36">
         <v>11.8</v>
@@ -4239,28 +4239,28 @@
         <v>34.89375</v>
       </c>
       <c r="M36">
-        <v>6.19364517035165</v>
+        <v>6.375811204773759</v>
       </c>
       <c r="N36">
-        <v>28.70010482964835</v>
+        <v>28.51793879522624</v>
       </c>
       <c r="O36">
-        <v>4.190215305128659</v>
+        <v>4.163619064103031</v>
       </c>
       <c r="P36">
-        <v>24.50988952451969</v>
+        <v>24.35431973112321</v>
       </c>
       <c r="Q36">
-        <v>31.73988952451969</v>
+        <v>31.58431973112321</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08184049538467472</v>
+        <v>0.08233874516627185</v>
       </c>
       <c r="T36">
-        <v>0.8323440042650052</v>
+        <v>0.8438509276275254</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.633798682403188</v>
+        <v>5.472833005763096</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07004935435807669</v>
+        <v>0.07002707376226809</v>
       </c>
       <c r="C37">
-        <v>223.2859846351632</v>
+        <v>220.2923693164728</v>
       </c>
       <c r="D37">
-        <v>326.7809431301679</v>
+        <v>327.0814694827633</v>
       </c>
       <c r="E37">
-        <v>-167.7192086335801</v>
+        <v>-164.4250669622942</v>
       </c>
       <c r="F37">
-        <v>115.2949584950047</v>
+        <v>118.5891001662905</v>
       </c>
       <c r="G37">
         <v>11.8</v>
@@ -4321,28 +4321,28 @@
         <v>34.89375</v>
       </c>
       <c r="M37">
-        <v>6.375811204773759</v>
+        <v>6.557977239195865</v>
       </c>
       <c r="N37">
-        <v>28.51793879522624</v>
+        <v>28.33577276080413</v>
       </c>
       <c r="O37">
-        <v>4.163619064103031</v>
+        <v>4.137022823077404</v>
       </c>
       <c r="P37">
-        <v>24.35431973112321</v>
+        <v>24.19874993772673</v>
       </c>
       <c r="Q37">
-        <v>31.58431973112321</v>
+        <v>31.42874993772673</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08233874516627185</v>
+        <v>0.0828525652535439</v>
       </c>
       <c r="T37">
-        <v>0.8438509276275254</v>
+        <v>0.8557174423451245</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.472833005763096</v>
+        <v>5.320809866714122</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07002707376226809</v>
+        <v>0.07000479316645948</v>
       </c>
       <c r="C38">
-        <v>220.2923693164728</v>
+        <v>217.2993072688761</v>
       </c>
       <c r="D38">
-        <v>327.0814694827633</v>
+        <v>327.3825491064525</v>
       </c>
       <c r="E38">
-        <v>-164.4250669622942</v>
+        <v>-161.1309252910084</v>
       </c>
       <c r="F38">
-        <v>118.5891001662905</v>
+        <v>121.8832418375763</v>
       </c>
       <c r="G38">
         <v>11.8</v>
@@ -4403,28 +4403,28 @@
         <v>34.89375</v>
       </c>
       <c r="M38">
-        <v>6.557977239195864</v>
+        <v>6.740143273617972</v>
       </c>
       <c r="N38">
-        <v>28.33577276080413</v>
+        <v>28.15360672638202</v>
       </c>
       <c r="O38">
-        <v>4.137022823077404</v>
+        <v>4.110426582051775</v>
       </c>
       <c r="P38">
-        <v>24.19874993772673</v>
+        <v>24.04318014433025</v>
       </c>
       <c r="Q38">
-        <v>31.42874993772673</v>
+        <v>31.27318014433025</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0828525652535439</v>
+        <v>0.08338269708961822</v>
       </c>
       <c r="T38">
-        <v>0.8557174423451245</v>
+        <v>0.8679606718156633</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.320809866714122</v>
+        <v>5.177004194640767</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07000479316645948</v>
+        <v>0.06998251257065087</v>
       </c>
       <c r="C39">
-        <v>217.2993072688761</v>
+        <v>214.3068000216446</v>
       </c>
       <c r="D39">
-        <v>327.3825491064525</v>
+        <v>327.6841835305068</v>
       </c>
       <c r="E39">
-        <v>-161.1309252910084</v>
+        <v>-157.8367836197226</v>
       </c>
       <c r="F39">
-        <v>121.8832418375763</v>
+        <v>125.1773835088622</v>
       </c>
       <c r="G39">
         <v>11.8</v>
@@ -4485,28 +4485,28 @@
         <v>34.89375</v>
       </c>
       <c r="M39">
-        <v>6.740143273617972</v>
+        <v>6.922309308040079</v>
       </c>
       <c r="N39">
-        <v>28.15360672638202</v>
+        <v>27.97144069195992</v>
       </c>
       <c r="O39">
-        <v>4.110426582051775</v>
+        <v>4.083830341026148</v>
       </c>
       <c r="P39">
-        <v>24.04318014433025</v>
+        <v>23.88761035093377</v>
       </c>
       <c r="Q39">
-        <v>31.27318014433025</v>
+        <v>31.11761035093377</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08338269708961822</v>
+        <v>0.08392992995266269</v>
       </c>
       <c r="T39">
-        <v>0.8679606718156633</v>
+        <v>0.8805988441723485</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.177004194640767</v>
+        <v>5.040767242150221</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06998251257065087</v>
+        <v>0.06996023197484225</v>
       </c>
       <c r="C40">
-        <v>214.3068000216446</v>
+        <v>211.3148491096911</v>
       </c>
       <c r="D40">
-        <v>327.6841835305068</v>
+        <v>327.9863742898391</v>
       </c>
       <c r="E40">
-        <v>-157.8367836197226</v>
+        <v>-154.5426419484367</v>
       </c>
       <c r="F40">
-        <v>125.1773835088622</v>
+        <v>128.471525180148</v>
       </c>
       <c r="G40">
         <v>11.8</v>
@@ -4567,28 +4567,28 @@
         <v>34.89375</v>
       </c>
       <c r="M40">
-        <v>6.922309308040079</v>
+        <v>7.104475342462186</v>
       </c>
       <c r="N40">
-        <v>27.97144069195992</v>
+        <v>27.78927465753781</v>
       </c>
       <c r="O40">
-        <v>4.083830341026148</v>
+        <v>4.05723410000052</v>
       </c>
       <c r="P40">
-        <v>23.88761035093377</v>
+        <v>23.73204055753729</v>
       </c>
       <c r="Q40">
-        <v>31.11761035093377</v>
+        <v>30.96204055753729</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08392992995266269</v>
+        <v>0.08449510487679059</v>
       </c>
       <c r="T40">
-        <v>0.8805988441723485</v>
+        <v>0.8936513828358102</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.040767242150221</v>
+        <v>4.911516800043805</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06996023197484225</v>
+        <v>0.06993795137903364</v>
       </c>
       <c r="C41">
-        <v>211.3148491096911</v>
+        <v>208.3234560735952</v>
       </c>
       <c r="D41">
-        <v>327.9863742898391</v>
+        <v>328.2891229250291</v>
       </c>
       <c r="E41">
-        <v>-154.5426419484367</v>
+        <v>-151.2485002771508</v>
       </c>
       <c r="F41">
-        <v>128.471525180148</v>
+        <v>131.7656668514339</v>
       </c>
       <c r="G41">
         <v>11.8</v>
@@ -4649,28 +4649,28 @@
         <v>34.89375</v>
       </c>
       <c r="M41">
-        <v>7.104475342462186</v>
+        <v>7.286641376884296</v>
       </c>
       <c r="N41">
-        <v>27.78927465753781</v>
+        <v>27.6071086231157</v>
       </c>
       <c r="O41">
-        <v>4.05723410000052</v>
+        <v>4.030637858974892</v>
       </c>
       <c r="P41">
-        <v>23.73204055753729</v>
+        <v>23.57647076414081</v>
       </c>
       <c r="Q41">
-        <v>30.96204055753729</v>
+        <v>30.80647076414081</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08449510487679059</v>
+        <v>0.08507911896505607</v>
       </c>
       <c r="T41">
-        <v>0.8936513828358102</v>
+        <v>0.9071390061213873</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.911516800043805</v>
+        <v>4.788728880042709</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06993795137903364</v>
+        <v>0.06991567078322503</v>
       </c>
       <c r="C42">
-        <v>208.3234560735952</v>
+        <v>205.3326224596304</v>
       </c>
       <c r="D42">
-        <v>328.2891229250291</v>
+        <v>328.5924309823502</v>
       </c>
       <c r="E42">
-        <v>-151.2485002771508</v>
+        <v>-147.954358605865</v>
       </c>
       <c r="F42">
-        <v>131.7656668514339</v>
+        <v>135.0598085227197</v>
       </c>
       <c r="G42">
         <v>11.8</v>
@@ -4731,28 +4731,28 @@
         <v>34.89375</v>
       </c>
       <c r="M42">
-        <v>7.286641376884296</v>
+        <v>7.468807411306402</v>
       </c>
       <c r="N42">
-        <v>27.6071086231157</v>
+        <v>27.4249425886936</v>
       </c>
       <c r="O42">
-        <v>4.030637858974892</v>
+        <v>4.004041617949265</v>
       </c>
       <c r="P42">
-        <v>23.57647076414081</v>
+        <v>23.42090097074433</v>
       </c>
       <c r="Q42">
-        <v>30.80647076414081</v>
+        <v>30.65090097074433</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08507911896505607</v>
+        <v>0.08568293014105938</v>
       </c>
       <c r="T42">
-        <v>0.9071390061213873</v>
+        <v>0.9210838369759671</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.788728880042709</v>
+        <v>4.671930614675814</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06991567078322503</v>
+        <v>0.06989339018741642</v>
       </c>
       <c r="C43">
-        <v>205.3326224596304</v>
+        <v>202.34234981979</v>
       </c>
       <c r="D43">
-        <v>328.5924309823502</v>
+        <v>328.8963000137956</v>
       </c>
       <c r="E43">
-        <v>-147.954358605865</v>
+        <v>-144.6602169345792</v>
       </c>
       <c r="F43">
-        <v>135.0598085227197</v>
+        <v>138.3539501940056</v>
       </c>
       <c r="G43">
         <v>11.8</v>
@@ -4813,28 +4813,28 @@
         <v>34.89375</v>
       </c>
       <c r="M43">
-        <v>7.468807411306402</v>
+        <v>7.65097344572851</v>
       </c>
       <c r="N43">
-        <v>27.4249425886936</v>
+        <v>27.24277655427149</v>
       </c>
       <c r="O43">
-        <v>4.004041617949265</v>
+        <v>3.977445376923637</v>
       </c>
       <c r="P43">
-        <v>23.42090097074433</v>
+        <v>23.26533117734785</v>
       </c>
       <c r="Q43">
-        <v>30.65090097074433</v>
+        <v>30.49533117734785</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08568293014105938</v>
+        <v>0.08630756239209728</v>
       </c>
       <c r="T43">
-        <v>0.9210838369759671</v>
+        <v>0.9355095240669117</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.671930614675814</v>
+        <v>4.560694171469247</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06989339018741643</v>
+        <v>0.07078915959160781</v>
       </c>
       <c r="C44">
-        <v>202.3423498197897</v>
+        <v>187.2584862243201</v>
       </c>
       <c r="D44">
-        <v>328.8963000137953</v>
+        <v>317.1065780896116</v>
       </c>
       <c r="E44">
-        <v>-144.6602169345792</v>
+        <v>-141.3660752632933</v>
       </c>
       <c r="F44">
-        <v>138.3539501940056</v>
+        <v>141.6480918652914</v>
       </c>
       <c r="G44">
         <v>11.8</v>
@@ -4895,45 +4895,45 @@
         <v>34.89375</v>
       </c>
       <c r="M44">
-        <v>7.65097344572851</v>
+        <v>8.187259709813846</v>
       </c>
       <c r="N44">
-        <v>27.24277655427149</v>
+        <v>26.70649029018615</v>
       </c>
       <c r="O44">
-        <v>3.977445376923637</v>
+        <v>3.899147582367178</v>
       </c>
       <c r="P44">
-        <v>23.26533117734785</v>
+        <v>22.80734270781898</v>
       </c>
       <c r="Q44">
-        <v>30.49533117734785</v>
+        <v>30.03734270781898</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08630756239209728</v>
+        <v>0.08695411156422422</v>
       </c>
       <c r="T44">
-        <v>0.9355095240669116</v>
+        <v>0.9504413756171876</v>
       </c>
       <c r="U44">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.146</v>
       </c>
       <c r="W44">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.560694171469247</v>
+        <v>4.261957142775599</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07078915959160781</v>
+        <v>0.0707882289957992</v>
       </c>
       <c r="C45">
-        <v>187.2584862243201</v>
+        <v>183.9761540355111</v>
       </c>
       <c r="D45">
-        <v>317.1065780896116</v>
+        <v>317.1183875720884</v>
       </c>
       <c r="E45">
-        <v>-141.3660752632933</v>
+        <v>-138.0719335920075</v>
       </c>
       <c r="F45">
-        <v>141.6480918652914</v>
+        <v>144.9422335365773</v>
       </c>
       <c r="G45">
         <v>11.8</v>
@@ -4977,28 +4977,28 @@
         <v>34.89375</v>
       </c>
       <c r="M45">
-        <v>8.187259709813846</v>
+        <v>8.377661098414167</v>
       </c>
       <c r="N45">
-        <v>26.70649029018615</v>
+        <v>26.51608890158583</v>
       </c>
       <c r="O45">
-        <v>3.899147582367178</v>
+        <v>3.871348979631531</v>
       </c>
       <c r="P45">
-        <v>22.80734270781898</v>
+        <v>22.6447399219543</v>
       </c>
       <c r="Q45">
-        <v>30.03734270781898</v>
+        <v>29.8747399219543</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08695411156422422</v>
+        <v>0.08762375177821284</v>
       </c>
       <c r="T45">
-        <v>0.9504413756171876</v>
+        <v>0.9659065075799733</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.261957142775599</v>
+        <v>4.165094480439791</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0707882289957992</v>
+        <v>0.07078729839999058</v>
       </c>
       <c r="C46">
-        <v>183.9761540355111</v>
+        <v>180.6938227263375</v>
       </c>
       <c r="D46">
-        <v>317.1183875720884</v>
+        <v>317.1301979342006</v>
       </c>
       <c r="E46">
-        <v>-138.0719335920075</v>
+        <v>-134.7777919207216</v>
       </c>
       <c r="F46">
-        <v>144.9422335365773</v>
+        <v>148.2363752078631</v>
       </c>
       <c r="G46">
         <v>11.8</v>
@@ -5059,28 +5059,28 @@
         <v>34.89375</v>
       </c>
       <c r="M46">
-        <v>8.377661098414167</v>
+        <v>8.568062487014489</v>
       </c>
       <c r="N46">
-        <v>26.51608890158583</v>
+        <v>26.32568751298551</v>
       </c>
       <c r="O46">
-        <v>3.871348979631531</v>
+        <v>3.843550376895884</v>
       </c>
       <c r="P46">
-        <v>22.6447399219543</v>
+        <v>22.48213713608963</v>
       </c>
       <c r="Q46">
-        <v>29.8747399219543</v>
+        <v>29.71213713608963</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08762375177821284</v>
+        <v>0.08831774254543742</v>
       </c>
       <c r="T46">
-        <v>0.9659065075799733</v>
+        <v>0.9819340079777695</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.165094480439791</v>
+        <v>4.072536825318906</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07078729839999058</v>
+        <v>0.07216130780418198</v>
       </c>
       <c r="C47">
-        <v>180.6938227263375</v>
+        <v>160.8701568921592</v>
       </c>
       <c r="D47">
-        <v>317.1301979342006</v>
+        <v>300.6006737713082</v>
       </c>
       <c r="E47">
-        <v>-134.7777919207216</v>
+        <v>-131.4836502494358</v>
       </c>
       <c r="F47">
-        <v>148.2363752078631</v>
+        <v>151.530516879149</v>
       </c>
       <c r="G47">
         <v>11.8</v>
@@ -5141,45 +5141,45 @@
         <v>34.89375</v>
       </c>
       <c r="M47">
-        <v>8.568062487014489</v>
+        <v>9.288820684691833</v>
       </c>
       <c r="N47">
-        <v>26.32568751298551</v>
+        <v>25.60492931530816</v>
       </c>
       <c r="O47">
-        <v>3.843550376895884</v>
+        <v>3.738319680034992</v>
       </c>
       <c r="P47">
-        <v>22.48213713608963</v>
+        <v>21.86660963527317</v>
       </c>
       <c r="Q47">
-        <v>29.71213713608963</v>
+        <v>29.09660963527317</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08831774254543742</v>
+        <v>0.08903743667441105</v>
       </c>
       <c r="T47">
-        <v>0.9819340079777695</v>
+        <v>0.9985551195014101</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.146</v>
       </c>
       <c r="W47">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.072536825318906</v>
+        <v>3.756531769151881</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07216130780418198</v>
+        <v>0.07219026720837338</v>
       </c>
       <c r="C48">
-        <v>160.8701568921592</v>
+        <v>157.2461505649676</v>
       </c>
       <c r="D48">
-        <v>300.6006737713082</v>
+        <v>300.2708091154025</v>
       </c>
       <c r="E48">
-        <v>-131.4836502494358</v>
+        <v>-128.1895085781499</v>
       </c>
       <c r="F48">
-        <v>151.530516879149</v>
+        <v>154.8246585504348</v>
       </c>
       <c r="G48">
         <v>11.8</v>
@@ -5223,28 +5223,28 @@
         <v>34.89375</v>
       </c>
       <c r="M48">
-        <v>9.288820684691833</v>
+        <v>9.490751569141656</v>
       </c>
       <c r="N48">
-        <v>25.60492931530816</v>
+        <v>25.40299843085834</v>
       </c>
       <c r="O48">
-        <v>3.738319680034992</v>
+        <v>3.708837770905317</v>
       </c>
       <c r="P48">
-        <v>21.86660963527317</v>
+        <v>21.69416065995302</v>
       </c>
       <c r="Q48">
-        <v>29.09660963527317</v>
+        <v>28.92416065995302</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08903743667441105</v>
+        <v>0.08978428907240257</v>
       </c>
       <c r="T48">
-        <v>0.9985551195014101</v>
+        <v>1.01580344278066</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.756531769151881</v>
+        <v>3.676605561297585</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07219026720837338</v>
+        <v>0.07221922661256475</v>
       </c>
       <c r="C49">
-        <v>157.2461505649676</v>
+        <v>153.622867399286</v>
       </c>
       <c r="D49">
-        <v>300.2708091154025</v>
+        <v>299.9416676210066</v>
       </c>
       <c r="E49">
-        <v>-128.1895085781499</v>
+        <v>-124.8953669068641</v>
       </c>
       <c r="F49">
-        <v>154.8246585504348</v>
+        <v>158.1188002217207</v>
       </c>
       <c r="G49">
         <v>11.8</v>
@@ -5305,28 +5305,28 @@
         <v>34.89375</v>
       </c>
       <c r="M49">
-        <v>9.490751569141656</v>
+        <v>9.692682453591477</v>
       </c>
       <c r="N49">
-        <v>25.40299843085834</v>
+        <v>25.20106754640852</v>
       </c>
       <c r="O49">
-        <v>3.708837770905317</v>
+        <v>3.679355861775644</v>
       </c>
       <c r="P49">
-        <v>21.69416065995302</v>
+        <v>21.52171168463288</v>
       </c>
       <c r="Q49">
-        <v>28.92416065995302</v>
+        <v>28.75171168463288</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08978428907240257</v>
+        <v>0.09055986656262452</v>
       </c>
       <c r="T49">
-        <v>1.01580344278066</v>
+        <v>1.033715163109111</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.676605561297585</v>
+        <v>3.600009612103886</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07221922661256475</v>
+        <v>0.07224818601675613</v>
       </c>
       <c r="C50">
-        <v>153.622867399286</v>
+        <v>150.0003050196395</v>
       </c>
       <c r="D50">
-        <v>299.9416676210066</v>
+        <v>299.613246912646</v>
       </c>
       <c r="E50">
-        <v>-124.8953669068641</v>
+        <v>-121.6012252355782</v>
       </c>
       <c r="F50">
-        <v>158.1188002217206</v>
+        <v>161.4129418930065</v>
       </c>
       <c r="G50">
         <v>11.8</v>
@@ -5387,28 +5387,28 @@
         <v>34.89375</v>
       </c>
       <c r="M50">
-        <v>9.692682453591475</v>
+        <v>9.894613338041299</v>
       </c>
       <c r="N50">
-        <v>25.20106754640852</v>
+        <v>24.9991366619587</v>
       </c>
       <c r="O50">
-        <v>3.679355861775644</v>
+        <v>3.64987395264597</v>
       </c>
       <c r="P50">
-        <v>21.52171168463288</v>
+        <v>21.34926270931273</v>
       </c>
       <c r="Q50">
-        <v>28.75171168463288</v>
+        <v>28.57926270931273</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09055986656262451</v>
+        <v>0.09136585885638457</v>
       </c>
       <c r="T50">
-        <v>1.033715163109111</v>
+        <v>1.0523293038426</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.600009612103887</v>
+        <v>3.526540028183399</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07224818601675613</v>
+        <v>0.07347274542094752</v>
       </c>
       <c r="C51">
-        <v>150.0003050196395</v>
+        <v>133.4478395519201</v>
       </c>
       <c r="D51">
-        <v>299.613246912646</v>
+        <v>286.3549231162125</v>
       </c>
       <c r="E51">
-        <v>-121.6012252355782</v>
+        <v>-118.3070835642924</v>
       </c>
       <c r="F51">
-        <v>161.4129418930065</v>
+        <v>164.7070835642924</v>
       </c>
       <c r="G51">
         <v>11.8</v>
@@ -5469,45 +5469,45 @@
         <v>34.89375</v>
       </c>
       <c r="M51">
-        <v>9.894613338041299</v>
+        <v>10.55772405647114</v>
       </c>
       <c r="N51">
-        <v>24.9991366619587</v>
+        <v>24.33602594352886</v>
       </c>
       <c r="O51">
-        <v>3.64987395264597</v>
+        <v>3.553059787755213</v>
       </c>
       <c r="P51">
-        <v>21.34926270931273</v>
+        <v>20.78296615577364</v>
       </c>
       <c r="Q51">
-        <v>28.57926270931273</v>
+        <v>28.01296615577364</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09136585885638457</v>
+        <v>0.09220409084189504</v>
       </c>
       <c r="T51">
-        <v>1.0523293038426</v>
+        <v>1.071688010205428</v>
       </c>
       <c r="U51">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V51">
         <v>0.146</v>
       </c>
       <c r="W51">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.526540028183399</v>
+        <v>3.305044705976435</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07347274542094752</v>
+        <v>0.0735256168251389</v>
       </c>
       <c r="C52">
-        <v>133.4478395519201</v>
+        <v>129.607632955271</v>
       </c>
       <c r="D52">
-        <v>286.3549231162125</v>
+        <v>285.8088581908492</v>
       </c>
       <c r="E52">
-        <v>-118.3070835642924</v>
+        <v>-115.0129418930065</v>
       </c>
       <c r="F52">
-        <v>164.7070835642924</v>
+        <v>168.0012252355782</v>
       </c>
       <c r="G52">
         <v>11.8</v>
@@ -5551,28 +5551,28 @@
         <v>34.89375</v>
       </c>
       <c r="M52">
-        <v>10.55772405647114</v>
+        <v>10.76887853760056</v>
       </c>
       <c r="N52">
-        <v>24.33602594352886</v>
+        <v>24.12487146239943</v>
       </c>
       <c r="O52">
-        <v>3.553059787755213</v>
+        <v>3.522231233510317</v>
       </c>
       <c r="P52">
-        <v>20.78296615577364</v>
+        <v>20.60264022888911</v>
       </c>
       <c r="Q52">
-        <v>28.01296615577364</v>
+        <v>27.83264022888912</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09220409084189504</v>
+        <v>0.0930765363778345</v>
       </c>
       <c r="T52">
-        <v>1.071688010205428</v>
+        <v>1.091836867848372</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.305044705976435</v>
+        <v>3.240239907820034</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0735256168251389</v>
+        <v>0.0735784882293303</v>
       </c>
       <c r="C53">
-        <v>129.607632955271</v>
+        <v>125.7695050332526</v>
       </c>
       <c r="D53">
-        <v>285.8088581908492</v>
+        <v>285.2648719401167</v>
       </c>
       <c r="E53">
-        <v>-115.0129418930065</v>
+        <v>-111.7188002217207</v>
       </c>
       <c r="F53">
-        <v>168.0012252355782</v>
+        <v>171.2953669068641</v>
       </c>
       <c r="G53">
         <v>11.8</v>
@@ -5633,28 +5633,28 @@
         <v>34.89375</v>
       </c>
       <c r="M53">
-        <v>10.76887853760056</v>
+        <v>10.98003301872999</v>
       </c>
       <c r="N53">
-        <v>24.12487146239943</v>
+        <v>23.91371698127001</v>
       </c>
       <c r="O53">
-        <v>3.522231233510317</v>
+        <v>3.491402679265421</v>
       </c>
       <c r="P53">
-        <v>20.60264022888911</v>
+        <v>20.42231430200459</v>
       </c>
       <c r="Q53">
-        <v>27.83264022888912</v>
+        <v>27.65231430200459</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0930765363778345</v>
+        <v>0.09398533381110478</v>
       </c>
       <c r="T53">
-        <v>1.091836867848372</v>
+        <v>1.112825261226438</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.240239907820034</v>
+        <v>3.177927601900418</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0735784882293303</v>
+        <v>0.07363135963352169</v>
       </c>
       <c r="C54">
-        <v>125.7695050332526</v>
+        <v>121.9334439392526</v>
       </c>
       <c r="D54">
-        <v>285.2648719401167</v>
+        <v>284.7229525174025</v>
       </c>
       <c r="E54">
-        <v>-111.7188002217207</v>
+        <v>-108.4246585504348</v>
       </c>
       <c r="F54">
-        <v>171.2953669068641</v>
+        <v>174.5895085781499</v>
       </c>
       <c r="G54">
         <v>11.8</v>
@@ -5715,28 +5715,28 @@
         <v>34.89375</v>
       </c>
       <c r="M54">
-        <v>10.98003301872999</v>
+        <v>11.19118749985941</v>
       </c>
       <c r="N54">
-        <v>23.91371698127001</v>
+        <v>23.70256250014059</v>
       </c>
       <c r="O54">
-        <v>3.491402679265421</v>
+        <v>3.460574125020525</v>
       </c>
       <c r="P54">
-        <v>20.42231430200459</v>
+        <v>20.24198837512006</v>
       </c>
       <c r="Q54">
-        <v>27.65231430200459</v>
+        <v>27.47198837512006</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09398533381110478</v>
+        <v>0.09493280347557806</v>
       </c>
       <c r="T54">
-        <v>1.112825261226438</v>
+        <v>1.134706777726976</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.177927601900418</v>
+        <v>3.117966703751354</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07363135963352169</v>
+        <v>0.07368423103771307</v>
       </c>
       <c r="C55">
-        <v>121.9334439392526</v>
+        <v>118.0994379165076</v>
       </c>
       <c r="D55">
-        <v>284.7229525174025</v>
+        <v>284.1830881659433</v>
       </c>
       <c r="E55">
-        <v>-108.4246585504348</v>
+        <v>-105.130516879149</v>
       </c>
       <c r="F55">
-        <v>174.5895085781499</v>
+        <v>177.8836502494358</v>
       </c>
       <c r="G55">
         <v>11.8</v>
@@ -5797,28 +5797,28 @@
         <v>34.89375</v>
       </c>
       <c r="M55">
-        <v>11.19118749985941</v>
+        <v>11.40234198098883</v>
       </c>
       <c r="N55">
-        <v>23.70256250014059</v>
+        <v>23.49140801901116</v>
       </c>
       <c r="O55">
-        <v>3.460574125020525</v>
+        <v>3.42974557077563</v>
       </c>
       <c r="P55">
-        <v>20.24198837512006</v>
+        <v>20.06166244823553</v>
       </c>
       <c r="Q55">
-        <v>27.47198837512006</v>
+        <v>27.29166244823553</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09493280347557806</v>
+        <v>0.09592146747328928</v>
       </c>
       <c r="T55">
-        <v>1.134706777726976</v>
+        <v>1.157539664510145</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.117966703751354</v>
+        <v>3.06022657960781</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07368423103771307</v>
+        <v>0.07373710244190446</v>
       </c>
       <c r="C56">
-        <v>118.0994379165076</v>
+        <v>114.267475297254</v>
       </c>
       <c r="D56">
-        <v>284.1830881659433</v>
+        <v>283.6452672179756</v>
       </c>
       <c r="E56">
-        <v>-105.130516879149</v>
+        <v>-101.8363752078631</v>
       </c>
       <c r="F56">
-        <v>177.8836502494358</v>
+        <v>181.1777919207216</v>
       </c>
       <c r="G56">
         <v>11.8</v>
@@ -5879,28 +5879,28 @@
         <v>34.89375</v>
       </c>
       <c r="M56">
-        <v>11.40234198098883</v>
+        <v>11.61349646211826</v>
       </c>
       <c r="N56">
-        <v>23.49140801901116</v>
+        <v>23.28025353788174</v>
       </c>
       <c r="O56">
-        <v>3.42974557077563</v>
+        <v>3.398917016530734</v>
       </c>
       <c r="P56">
-        <v>20.06166244823553</v>
+        <v>19.88133652135101</v>
       </c>
       <c r="Q56">
-        <v>27.29166244823553</v>
+        <v>27.11133652135101</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09592146747328928</v>
+        <v>0.09695407209312103</v>
       </c>
       <c r="T56">
-        <v>1.157539664510145</v>
+        <v>1.181387346261456</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.06022657960781</v>
+        <v>3.004586096342214</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07373710244190446</v>
+        <v>0.07752024584609585</v>
       </c>
       <c r="C57">
-        <v>114.267475297254</v>
+        <v>77.1441279189176</v>
       </c>
       <c r="D57">
-        <v>283.6452672179756</v>
+        <v>249.8160615109251</v>
       </c>
       <c r="E57">
-        <v>-101.8363752078631</v>
+        <v>-98.54223353657727</v>
       </c>
       <c r="F57">
-        <v>181.1777919207216</v>
+        <v>184.4719335920075</v>
       </c>
       <c r="G57">
         <v>11.8</v>
@@ -5961,45 +5961,45 @@
         <v>34.89375</v>
       </c>
       <c r="M57">
-        <v>11.61349646211826</v>
+        <v>13.26353202526534</v>
       </c>
       <c r="N57">
-        <v>23.28025353788174</v>
+        <v>21.63021797473466</v>
       </c>
       <c r="O57">
-        <v>3.398917016530734</v>
+        <v>3.15801182431126</v>
       </c>
       <c r="P57">
-        <v>19.88133652135101</v>
+        <v>18.4722061504234</v>
       </c>
       <c r="Q57">
-        <v>27.11133652135101</v>
+        <v>25.7022061504234</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09695407209312103</v>
+        <v>0.09803361328658149</v>
       </c>
       <c r="T57">
-        <v>1.181387346261456</v>
+        <v>1.206319013546917</v>
       </c>
       <c r="U57">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V57">
         <v>0.146</v>
       </c>
       <c r="W57">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.004586096342214</v>
+        <v>2.630803765809277</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07752024584609585</v>
+        <v>0.07763972925028724</v>
       </c>
       <c r="C58">
-        <v>77.1441279189176</v>
+        <v>72.91251365744819</v>
       </c>
       <c r="D58">
-        <v>249.8160615109251</v>
+        <v>248.8785889207415</v>
       </c>
       <c r="E58">
-        <v>-98.54223353657727</v>
+        <v>-95.24809186529143</v>
       </c>
       <c r="F58">
-        <v>184.4719335920075</v>
+        <v>187.7660752632933</v>
       </c>
       <c r="G58">
         <v>11.8</v>
@@ -6043,28 +6043,28 @@
         <v>34.89375</v>
       </c>
       <c r="M58">
-        <v>13.26353202526534</v>
+        <v>13.50038081143079</v>
       </c>
       <c r="N58">
-        <v>21.63021797473466</v>
+        <v>21.39336918856921</v>
       </c>
       <c r="O58">
-        <v>3.15801182431126</v>
+        <v>3.123431901531104</v>
       </c>
       <c r="P58">
-        <v>18.4722061504234</v>
+        <v>18.2699372870381</v>
       </c>
       <c r="Q58">
-        <v>25.7022061504234</v>
+        <v>25.4999372870381</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09803361328658149</v>
+        <v>0.09916336569834241</v>
       </c>
       <c r="T58">
-        <v>1.206319013546917</v>
+        <v>1.232410293264259</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.630803765809277</v>
+        <v>2.584649313777535</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07763972925028724</v>
+        <v>0.07775921265447862</v>
       </c>
       <c r="C59">
-        <v>72.91251365744819</v>
+        <v>68.68790910661357</v>
       </c>
       <c r="D59">
-        <v>248.8785889207415</v>
+        <v>247.9481260411928</v>
       </c>
       <c r="E59">
-        <v>-95.24809186529143</v>
+        <v>-91.95395019400559</v>
       </c>
       <c r="F59">
-        <v>187.7660752632933</v>
+        <v>191.0602169345792</v>
       </c>
       <c r="G59">
         <v>11.8</v>
@@ -6125,28 +6125,28 @@
         <v>34.89375</v>
       </c>
       <c r="M59">
-        <v>13.50038081143079</v>
+        <v>13.73722959759624</v>
       </c>
       <c r="N59">
-        <v>21.39336918856921</v>
+        <v>21.15652040240376</v>
       </c>
       <c r="O59">
-        <v>3.123431901531104</v>
+        <v>3.088851978750948</v>
       </c>
       <c r="P59">
-        <v>18.2699372870381</v>
+        <v>18.06766842365281</v>
       </c>
       <c r="Q59">
-        <v>25.4999372870381</v>
+        <v>25.29766842365281</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09916336569834241</v>
+        <v>0.1003469158439967</v>
       </c>
       <c r="T59">
-        <v>1.232410293264259</v>
+        <v>1.259744014872904</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.584649313777535</v>
+        <v>2.540086394574475</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07775921265447862</v>
+        <v>0.07984375005867002</v>
       </c>
       <c r="C60">
-        <v>68.6879091066136</v>
+        <v>50.21162263220555</v>
       </c>
       <c r="D60">
-        <v>247.9481260411928</v>
+        <v>232.7659812380705</v>
       </c>
       <c r="E60">
-        <v>-91.95395019400561</v>
+        <v>-88.65980852271977</v>
       </c>
       <c r="F60">
-        <v>191.0602169345791</v>
+        <v>194.354358605865</v>
       </c>
       <c r="G60">
         <v>11.8</v>
@@ -6207,45 +6207,45 @@
         <v>34.89375</v>
       </c>
       <c r="M60">
-        <v>13.73722959759624</v>
+        <v>14.73206038232457</v>
       </c>
       <c r="N60">
-        <v>21.15652040240376</v>
+        <v>20.16168961767543</v>
       </c>
       <c r="O60">
-        <v>3.088851978750948</v>
+        <v>2.943606684180613</v>
       </c>
       <c r="P60">
-        <v>18.06766842365281</v>
+        <v>17.21808293349482</v>
       </c>
       <c r="Q60">
-        <v>25.29766842365281</v>
+        <v>24.44808293349482</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1003469158439967</v>
+        <v>0.1015882001430976</v>
       </c>
       <c r="T60">
-        <v>1.259744014872904</v>
+        <v>1.288411088755141</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.146</v>
       </c>
       <c r="W60">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.540086394574475</v>
+        <v>2.368558714425669</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07984375005867002</v>
+        <v>0.07999653946286139</v>
       </c>
       <c r="C61">
-        <v>50.21162263220555</v>
+        <v>45.87748755375023</v>
       </c>
       <c r="D61">
-        <v>232.7659812380705</v>
+        <v>231.725987830901</v>
       </c>
       <c r="E61">
-        <v>-88.65980852271977</v>
+        <v>-85.36566685143393</v>
       </c>
       <c r="F61">
-        <v>194.354358605865</v>
+        <v>197.6485002771508</v>
       </c>
       <c r="G61">
         <v>11.8</v>
@@ -6289,28 +6289,28 @@
         <v>34.89375</v>
       </c>
       <c r="M61">
-        <v>14.73206038232457</v>
+        <v>14.98175632100803</v>
       </c>
       <c r="N61">
-        <v>20.16168961767543</v>
+        <v>19.91199367899196</v>
       </c>
       <c r="O61">
-        <v>2.943606684180613</v>
+        <v>2.907151077132826</v>
       </c>
       <c r="P61">
-        <v>17.21808293349482</v>
+        <v>17.00484260185913</v>
       </c>
       <c r="Q61">
-        <v>24.44808293349482</v>
+        <v>24.23484260185914</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1015882001430976</v>
+        <v>0.1028915486571535</v>
       </c>
       <c r="T61">
-        <v>1.288411088755141</v>
+        <v>1.31851151633149</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.368558714425669</v>
+        <v>2.329082735851907</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07999653946286139</v>
+        <v>0.08014932886705278</v>
       </c>
       <c r="C62">
-        <v>45.87748755375023</v>
+        <v>41.55260447399675</v>
       </c>
       <c r="D62">
-        <v>231.725987830901</v>
+        <v>230.6952464224334</v>
       </c>
       <c r="E62">
-        <v>-85.36566685143393</v>
+        <v>-82.07152518014806</v>
       </c>
       <c r="F62">
-        <v>197.6485002771508</v>
+        <v>200.9426419484367</v>
       </c>
       <c r="G62">
         <v>11.8</v>
@@ -6371,28 +6371,28 @@
         <v>34.89375</v>
       </c>
       <c r="M62">
-        <v>14.98175632100803</v>
+        <v>15.2314522596915</v>
       </c>
       <c r="N62">
-        <v>19.91199367899196</v>
+        <v>19.6622977403085</v>
       </c>
       <c r="O62">
-        <v>2.907151077132826</v>
+        <v>2.87069547008504</v>
       </c>
       <c r="P62">
-        <v>17.00484260185913</v>
+        <v>16.79160227022346</v>
       </c>
       <c r="Q62">
-        <v>24.23484260185914</v>
+        <v>24.02160227022346</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1028915486571535</v>
+        <v>0.1042617355565456</v>
       </c>
       <c r="T62">
-        <v>1.31851151633149</v>
+        <v>1.350155555578421</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.329082735851907</v>
+        <v>2.290901051657614</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08014932886705278</v>
+        <v>0.08030211827124419</v>
       </c>
       <c r="C63">
-        <v>41.55260447399675</v>
+        <v>37.23685047811196</v>
       </c>
       <c r="D63">
-        <v>230.6952464224334</v>
+        <v>229.6736340978345</v>
       </c>
       <c r="E63">
-        <v>-82.07152518014806</v>
+        <v>-78.77738350886221</v>
       </c>
       <c r="F63">
-        <v>200.9426419484367</v>
+        <v>204.2367836197225</v>
       </c>
       <c r="G63">
         <v>11.8</v>
@@ -6453,28 +6453,28 @@
         <v>34.89375</v>
       </c>
       <c r="M63">
-        <v>15.2314522596915</v>
+        <v>15.48114819837497</v>
       </c>
       <c r="N63">
-        <v>19.6622977403085</v>
+        <v>19.41260180162503</v>
       </c>
       <c r="O63">
-        <v>2.87069547008504</v>
+        <v>2.834239863037254</v>
       </c>
       <c r="P63">
-        <v>16.79160227022346</v>
+        <v>16.57836193858778</v>
       </c>
       <c r="Q63">
-        <v>24.02160227022346</v>
+        <v>23.80836193858778</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1042617355565456</v>
+        <v>0.1057040375559057</v>
       </c>
       <c r="T63">
-        <v>1.350155555578421</v>
+        <v>1.38346507057519</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.290901051657614</v>
+        <v>2.253951034695394</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08030211827124419</v>
+        <v>0.08045490767543556</v>
       </c>
       <c r="C64">
-        <v>37.23685047811196</v>
+        <v>32.9301048189312</v>
       </c>
       <c r="D64">
-        <v>229.6736340978345</v>
+        <v>228.6610301099396</v>
       </c>
       <c r="E64">
-        <v>-78.77738350886221</v>
+        <v>-75.48324183757637</v>
       </c>
       <c r="F64">
-        <v>204.2367836197225</v>
+        <v>207.5309252910084</v>
       </c>
       <c r="G64">
         <v>11.8</v>
@@ -6535,28 +6535,28 @@
         <v>34.89375</v>
       </c>
       <c r="M64">
-        <v>15.48114819837497</v>
+        <v>15.73084413705844</v>
       </c>
       <c r="N64">
-        <v>19.41260180162503</v>
+        <v>19.16290586294156</v>
       </c>
       <c r="O64">
-        <v>2.834239863037254</v>
+        <v>2.797784255989468</v>
       </c>
       <c r="P64">
-        <v>16.57836193858778</v>
+        <v>16.36512160695209</v>
       </c>
       <c r="Q64">
-        <v>23.80836193858778</v>
+        <v>23.59512160695209</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1057040375559057</v>
+        <v>0.1072243018255015</v>
       </c>
       <c r="T64">
-        <v>1.38346507057519</v>
+        <v>1.418575099896109</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.253951034695394</v>
+        <v>2.218174034144674</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08045490767543556</v>
+        <v>0.08060769707962695</v>
       </c>
       <c r="C65">
-        <v>32.9301048189312</v>
+        <v>28.63224886938201</v>
       </c>
       <c r="D65">
-        <v>228.6610301099396</v>
+        <v>227.6573158316762</v>
       </c>
       <c r="E65">
-        <v>-75.48324183757637</v>
+        <v>-72.18910016629053</v>
       </c>
       <c r="F65">
-        <v>207.5309252910084</v>
+        <v>210.8250669622942</v>
       </c>
       <c r="G65">
         <v>11.8</v>
@@ -6617,28 +6617,28 @@
         <v>34.89375</v>
       </c>
       <c r="M65">
-        <v>15.73084413705844</v>
+        <v>15.9805400757419</v>
       </c>
       <c r="N65">
-        <v>19.16290586294156</v>
+        <v>18.91320992425809</v>
       </c>
       <c r="O65">
-        <v>2.797784255989468</v>
+        <v>2.761328648941682</v>
       </c>
       <c r="P65">
-        <v>16.36512160695209</v>
+        <v>16.15188127531641</v>
       </c>
       <c r="Q65">
-        <v>23.59512160695209</v>
+        <v>23.38188127531641</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1072243018255015</v>
+        <v>0.108829025221186</v>
       </c>
       <c r="T65">
-        <v>1.418575099896109</v>
+        <v>1.455635686401524</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.218174034144674</v>
+        <v>2.183515064861163</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08060769707962695</v>
+        <v>0.08076048648381834</v>
       </c>
       <c r="C66">
-        <v>28.63224886938201</v>
+        <v>24.34316607615747</v>
       </c>
       <c r="D66">
-        <v>227.6573158316762</v>
+        <v>226.6623747097375</v>
       </c>
       <c r="E66">
-        <v>-72.18910016629053</v>
+        <v>-68.89495849500466</v>
       </c>
       <c r="F66">
-        <v>210.8250669622942</v>
+        <v>214.1192086335801</v>
       </c>
       <c r="G66">
         <v>11.8</v>
@@ -6699,28 +6699,28 @@
         <v>34.89375</v>
       </c>
       <c r="M66">
-        <v>15.9805400757419</v>
+        <v>16.23023601442537</v>
       </c>
       <c r="N66">
-        <v>18.91320992425809</v>
+        <v>18.66351398557462</v>
       </c>
       <c r="O66">
-        <v>2.761328648941682</v>
+        <v>2.724873041893895</v>
       </c>
       <c r="P66">
-        <v>16.15188127531641</v>
+        <v>15.93864094368073</v>
       </c>
       <c r="Q66">
-        <v>23.38188127531641</v>
+        <v>23.16864094368073</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.108829025221186</v>
+        <v>0.1105254470966238</v>
       </c>
       <c r="T66">
-        <v>1.455635686401524</v>
+        <v>1.494814020707248</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.183515064861163</v>
+        <v>2.14992252540176</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08076048648381834</v>
+        <v>0.08091327588800973</v>
       </c>
       <c r="C67">
-        <v>24.34316607615747</v>
+        <v>20.06274191459755</v>
       </c>
       <c r="D67">
-        <v>226.6623747097375</v>
+        <v>225.6760922194635</v>
       </c>
       <c r="E67">
-        <v>-68.89495849500466</v>
+        <v>-65.60081682371882</v>
       </c>
       <c r="F67">
-        <v>214.1192086335801</v>
+        <v>217.4133503048659</v>
       </c>
       <c r="G67">
         <v>11.8</v>
@@ -6781,28 +6781,28 @@
         <v>34.89375</v>
       </c>
       <c r="M67">
-        <v>16.23023601442537</v>
+        <v>16.47993195310884</v>
       </c>
       <c r="N67">
-        <v>18.66351398557462</v>
+        <v>18.41381804689116</v>
       </c>
       <c r="O67">
-        <v>2.724873041893895</v>
+        <v>2.688417434846109</v>
       </c>
       <c r="P67">
-        <v>15.93864094368073</v>
+        <v>15.72540061204505</v>
       </c>
       <c r="Q67">
-        <v>23.16864094368073</v>
+        <v>22.95540061204505</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1105254470966238</v>
+        <v>0.1123216584941463</v>
       </c>
       <c r="T67">
-        <v>1.494814020707248</v>
+        <v>1.536296962913309</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.14992252540176</v>
+        <v>2.117347941683552</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08091327588800973</v>
+        <v>0.08106606529220112</v>
       </c>
       <c r="C68">
-        <v>20.06274191459755</v>
+        <v>15.79086384474394</v>
       </c>
       <c r="D68">
-        <v>225.6760922194635</v>
+        <v>224.6983558208957</v>
       </c>
       <c r="E68">
-        <v>-65.60081682371882</v>
+        <v>-62.30667515243297</v>
       </c>
       <c r="F68">
-        <v>217.4133503048659</v>
+        <v>220.7074919761518</v>
       </c>
       <c r="G68">
         <v>11.8</v>
@@ -6863,28 +6863,28 @@
         <v>34.89375</v>
       </c>
       <c r="M68">
-        <v>16.47993195310884</v>
+        <v>16.7296278917923</v>
       </c>
       <c r="N68">
-        <v>18.41381804689116</v>
+        <v>18.16412210820769</v>
       </c>
       <c r="O68">
-        <v>2.688417434846109</v>
+        <v>2.651961827798323</v>
       </c>
       <c r="P68">
-        <v>15.72540061204505</v>
+        <v>15.51216028040937</v>
       </c>
       <c r="Q68">
-        <v>22.95540061204505</v>
+        <v>22.74216028040937</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1123216584941463</v>
+        <v>0.1142267311884883</v>
       </c>
       <c r="T68">
-        <v>1.536296962913309</v>
+        <v>1.580294022828828</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.117347941683552</v>
+        <v>2.085745733598723</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08106606529220112</v>
+        <v>0.08121885469639251</v>
       </c>
       <c r="C69">
-        <v>15.79086384474394</v>
+        <v>11.52742126853198</v>
       </c>
       <c r="D69">
-        <v>224.6983558208957</v>
+        <v>223.7290549159696</v>
       </c>
       <c r="E69">
-        <v>-62.30667515243297</v>
+        <v>-59.01253348114713</v>
       </c>
       <c r="F69">
-        <v>220.7074919761518</v>
+        <v>224.0016336474376</v>
       </c>
       <c r="G69">
         <v>11.8</v>
@@ -6945,28 +6945,28 @@
         <v>34.89375</v>
       </c>
       <c r="M69">
-        <v>16.7296278917923</v>
+        <v>16.97932383047577</v>
       </c>
       <c r="N69">
-        <v>18.16412210820769</v>
+        <v>17.91442616952422</v>
       </c>
       <c r="O69">
-        <v>2.651961827798323</v>
+        <v>2.615506220750536</v>
       </c>
       <c r="P69">
-        <v>15.51216028040937</v>
+        <v>15.29891994877369</v>
       </c>
       <c r="Q69">
-        <v>22.74216028040937</v>
+        <v>22.52891994877369</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1142267311884883</v>
+        <v>0.1162508709262266</v>
       </c>
       <c r="T69">
-        <v>1.580294022828828</v>
+        <v>1.627040898989067</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.085745733598723</v>
+        <v>2.055073002222271</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08121885469639251</v>
+        <v>0.0813716441005839</v>
       </c>
       <c r="C70">
-        <v>11.52742126853198</v>
+        <v>7.272305488086175</v>
       </c>
       <c r="D70">
-        <v>223.7290549159696</v>
+        <v>222.7680808068096</v>
       </c>
       <c r="E70">
-        <v>-59.01253348114713</v>
+        <v>-55.71839180986126</v>
       </c>
       <c r="F70">
-        <v>224.0016336474376</v>
+        <v>227.2957753187235</v>
       </c>
       <c r="G70">
         <v>11.8</v>
@@ -7027,28 +7027,28 @@
         <v>34.89375</v>
       </c>
       <c r="M70">
-        <v>16.97932383047577</v>
+        <v>17.22901976915924</v>
       </c>
       <c r="N70">
-        <v>17.91442616952422</v>
+        <v>17.66473023084076</v>
       </c>
       <c r="O70">
-        <v>2.615506220750536</v>
+        <v>2.57905061370275</v>
       </c>
       <c r="P70">
-        <v>15.29891994877369</v>
+        <v>15.08567961713801</v>
       </c>
       <c r="Q70">
-        <v>22.52891994877369</v>
+        <v>22.31567961713801</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1162508709262266</v>
+        <v>0.1184056003244642</v>
       </c>
       <c r="T70">
-        <v>1.627040898989067</v>
+        <v>1.676803702643515</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.055073002222271</v>
+        <v>2.025289335523397</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0813716441005839</v>
+        <v>0.09001319350477528</v>
       </c>
       <c r="C71">
-        <v>7.272305488086175</v>
+        <v>-39.56226435337985</v>
       </c>
       <c r="D71">
-        <v>222.7680808068096</v>
+        <v>179.2276526366295</v>
       </c>
       <c r="E71">
-        <v>-55.71839180986126</v>
+        <v>-52.42425013857542</v>
       </c>
       <c r="F71">
-        <v>227.2957753187235</v>
+        <v>230.5899169900093</v>
       </c>
       <c r="G71">
         <v>11.8</v>
@@ -7109,45 +7109,45 @@
         <v>34.89375</v>
       </c>
       <c r="M71">
-        <v>17.22901976915924</v>
+        <v>20.75309252910084</v>
       </c>
       <c r="N71">
-        <v>17.66473023084076</v>
+        <v>14.14065747089916</v>
       </c>
       <c r="O71">
-        <v>2.57905061370275</v>
+        <v>2.064535990751277</v>
       </c>
       <c r="P71">
-        <v>15.08567961713801</v>
+        <v>12.07612148014788</v>
       </c>
       <c r="Q71">
-        <v>22.31567961713801</v>
+        <v>19.30612148014788</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1184056003244642</v>
+        <v>0.120703978349251</v>
       </c>
       <c r="T71">
-        <v>1.676803702643515</v>
+        <v>1.729884026541592</v>
       </c>
       <c r="U71">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V71">
         <v>0.146</v>
       </c>
       <c r="W71">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.025289335523397</v>
+        <v>1.681375917881663</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09001319350477528</v>
+        <v>0.09028725090896667</v>
       </c>
       <c r="C72">
-        <v>-39.56226435337985</v>
+        <v>-43.96051257738168</v>
       </c>
       <c r="D72">
-        <v>179.2276526366295</v>
+        <v>178.1235460839135</v>
       </c>
       <c r="E72">
-        <v>-52.42425013857542</v>
+        <v>-49.13010846728957</v>
       </c>
       <c r="F72">
-        <v>230.5899169900093</v>
+        <v>233.8840586612952</v>
       </c>
       <c r="G72">
         <v>11.8</v>
@@ -7191,28 +7191,28 @@
         <v>34.89375</v>
       </c>
       <c r="M72">
-        <v>20.75309252910084</v>
+        <v>21.04956527951656</v>
       </c>
       <c r="N72">
-        <v>14.14065747089916</v>
+        <v>13.84418472048343</v>
       </c>
       <c r="O72">
-        <v>2.064535990751277</v>
+        <v>2.021250969190581</v>
       </c>
       <c r="P72">
-        <v>12.07612148014788</v>
+        <v>11.82293375129285</v>
       </c>
       <c r="Q72">
-        <v>19.30612148014788</v>
+        <v>19.05293375129285</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.120703978349251</v>
+        <v>0.1231608652033334</v>
       </c>
       <c r="T72">
-        <v>1.729884026541592</v>
+        <v>1.786625062432641</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.681375917881663</v>
+        <v>1.657694566925583</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09028725090896667</v>
+        <v>0.09056130831315806</v>
       </c>
       <c r="C73">
-        <v>-43.96051257738165</v>
+        <v>-48.34524070614094</v>
       </c>
       <c r="D73">
-        <v>178.1235460839135</v>
+        <v>177.03295962644</v>
       </c>
       <c r="E73">
-        <v>-49.1301084672896</v>
+        <v>-45.83596679600376</v>
       </c>
       <c r="F73">
-        <v>233.8840586612951</v>
+        <v>237.178200332581</v>
       </c>
       <c r="G73">
         <v>11.8</v>
@@ -7273,28 +7273,28 @@
         <v>34.89375</v>
       </c>
       <c r="M73">
-        <v>21.04956527951656</v>
+        <v>21.34603802993229</v>
       </c>
       <c r="N73">
-        <v>13.84418472048344</v>
+        <v>13.54771197006771</v>
       </c>
       <c r="O73">
-        <v>2.021250969190582</v>
+        <v>1.977965947629885</v>
       </c>
       <c r="P73">
-        <v>11.82293375129285</v>
+        <v>11.56974602243782</v>
       </c>
       <c r="Q73">
-        <v>19.05293375129285</v>
+        <v>18.79974602243782</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1231608652033333</v>
+        <v>0.1257932439755645</v>
       </c>
       <c r="T73">
-        <v>1.786625062432641</v>
+        <v>1.847419029458764</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.657694566925583</v>
+        <v>1.634671031273839</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09056130831315806</v>
+        <v>0.09083536571734943</v>
       </c>
       <c r="C74">
-        <v>-48.34524070614094</v>
+        <v>-52.71669556449046</v>
       </c>
       <c r="D74">
-        <v>177.03295962644</v>
+        <v>175.9556464393764</v>
       </c>
       <c r="E74">
-        <v>-45.83596679600376</v>
+        <v>-42.54182512471792</v>
       </c>
       <c r="F74">
-        <v>237.178200332581</v>
+        <v>240.4723420038668</v>
       </c>
       <c r="G74">
         <v>11.8</v>
@@ -7355,28 +7355,28 @@
         <v>34.89375</v>
       </c>
       <c r="M74">
-        <v>21.34603802993229</v>
+        <v>21.64251078034802</v>
       </c>
       <c r="N74">
-        <v>13.54771197006771</v>
+        <v>13.25123921965198</v>
       </c>
       <c r="O74">
-        <v>1.977965947629885</v>
+        <v>1.934680926069189</v>
       </c>
       <c r="P74">
-        <v>11.56974602243782</v>
+        <v>11.31655829358279</v>
       </c>
       <c r="Q74">
-        <v>18.79974602243782</v>
+        <v>18.54655829358279</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1257932439755645</v>
+        <v>0.1286206137679609</v>
       </c>
       <c r="T74">
-        <v>1.847419029458764</v>
+        <v>1.912716253301637</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.634671031273839</v>
+        <v>1.612278277420772</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09083536571734943</v>
+        <v>0.09110942312154083</v>
       </c>
       <c r="C75">
-        <v>-52.71669556449046</v>
+        <v>-57.07511800551029</v>
       </c>
       <c r="D75">
-        <v>175.9556464393764</v>
+        <v>174.8913656696424</v>
       </c>
       <c r="E75">
-        <v>-42.54182512471792</v>
+        <v>-39.24768345343205</v>
       </c>
       <c r="F75">
-        <v>240.4723420038668</v>
+        <v>243.7664836751527</v>
       </c>
       <c r="G75">
         <v>11.8</v>
@@ -7437,28 +7437,28 @@
         <v>34.89375</v>
       </c>
       <c r="M75">
-        <v>21.64251078034802</v>
+        <v>21.93898353076374</v>
       </c>
       <c r="N75">
-        <v>13.25123921965198</v>
+        <v>12.95476646923625</v>
       </c>
       <c r="O75">
-        <v>1.934680926069189</v>
+        <v>1.891395904508493</v>
       </c>
       <c r="P75">
-        <v>11.31655829358279</v>
+        <v>11.06337056472776</v>
       </c>
       <c r="Q75">
-        <v>18.54655829358279</v>
+        <v>18.29337056472776</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1286206137679609</v>
+        <v>0.1316654735443878</v>
       </c>
       <c r="T75">
-        <v>1.912716253301637</v>
+        <v>1.983036340517039</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.612278277420772</v>
+        <v>1.590490733131303</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09110942312154083</v>
+        <v>0.09138348052573222</v>
       </c>
       <c r="C76">
-        <v>-57.07511800551029</v>
+        <v>-61.42074309004391</v>
       </c>
       <c r="D76">
-        <v>174.8913656696424</v>
+        <v>173.8398822563946</v>
       </c>
       <c r="E76">
-        <v>-39.24768345343205</v>
+        <v>-35.9535417821462</v>
       </c>
       <c r="F76">
-        <v>243.7664836751527</v>
+        <v>247.0606253464385</v>
       </c>
       <c r="G76">
         <v>11.8</v>
@@ -7519,28 +7519,28 @@
         <v>34.89375</v>
       </c>
       <c r="M76">
-        <v>21.93898353076374</v>
+        <v>22.23545628117947</v>
       </c>
       <c r="N76">
-        <v>12.95476646923625</v>
+        <v>12.65829371882053</v>
       </c>
       <c r="O76">
-        <v>1.891395904508493</v>
+        <v>1.848110882947797</v>
       </c>
       <c r="P76">
-        <v>11.06337056472776</v>
+        <v>10.81018283587273</v>
       </c>
       <c r="Q76">
-        <v>18.29337056472776</v>
+        <v>18.04018283587273</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1316654735443878</v>
+        <v>0.1349539221029289</v>
       </c>
       <c r="T76">
-        <v>1.983036340517039</v>
+        <v>2.058982034709674</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.590490733131303</v>
+        <v>1.569284190022885</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09138348052573222</v>
+        <v>0.09165753792992361</v>
       </c>
       <c r="C77">
-        <v>-61.42074309004391</v>
+        <v>-65.75380025977904</v>
       </c>
       <c r="D77">
-        <v>173.8398822563946</v>
+        <v>172.8009667579453</v>
       </c>
       <c r="E77">
-        <v>-35.9535417821462</v>
+        <v>-32.65940011086036</v>
       </c>
       <c r="F77">
-        <v>247.0606253464385</v>
+        <v>250.3547670177244</v>
       </c>
       <c r="G77">
         <v>11.8</v>
@@ -7601,28 +7601,28 @@
         <v>34.89375</v>
       </c>
       <c r="M77">
-        <v>22.23545628117947</v>
+        <v>22.53192903159519</v>
       </c>
       <c r="N77">
-        <v>12.65829371882053</v>
+        <v>12.3618209684048</v>
       </c>
       <c r="O77">
-        <v>1.848110882947797</v>
+        <v>1.804825861387101</v>
       </c>
       <c r="P77">
-        <v>10.81018283587273</v>
+        <v>10.5569951070177</v>
       </c>
       <c r="Q77">
-        <v>18.04018283587273</v>
+        <v>17.7869951070177</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1349539221029289</v>
+        <v>0.1385164080413484</v>
       </c>
       <c r="T77">
-        <v>2.058982034709674</v>
+        <v>2.141256536751694</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.569284190022885</v>
+        <v>1.548635713838374</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09165753792992361</v>
+        <v>0.09193159533411499</v>
       </c>
       <c r="C78">
-        <v>-65.75380025977904</v>
+        <v>-70.07451350415818</v>
       </c>
       <c r="D78">
-        <v>172.8009667579453</v>
+        <v>171.7743951848521</v>
       </c>
       <c r="E78">
-        <v>-32.65940011086036</v>
+        <v>-29.36525843957449</v>
       </c>
       <c r="F78">
-        <v>250.3547670177244</v>
+        <v>253.6489086890103</v>
       </c>
       <c r="G78">
         <v>11.8</v>
@@ -7683,28 +7683,28 @@
         <v>34.89375</v>
       </c>
       <c r="M78">
-        <v>22.53192903159519</v>
+        <v>22.82840178201092</v>
       </c>
       <c r="N78">
-        <v>12.3618209684048</v>
+        <v>12.06534821798908</v>
       </c>
       <c r="O78">
-        <v>1.804825861387101</v>
+        <v>1.761540839826405</v>
       </c>
       <c r="P78">
-        <v>10.5569951070177</v>
+        <v>10.30380737816267</v>
       </c>
       <c r="Q78">
-        <v>17.7869951070177</v>
+        <v>17.53380737816267</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1385164080413484</v>
+        <v>0.1423886753657174</v>
       </c>
       <c r="T78">
-        <v>2.141256536751694</v>
+        <v>2.230685343319108</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.548635713838374</v>
+        <v>1.528523561710602</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09193159533411499</v>
+        <v>0.09220565273830639</v>
       </c>
       <c r="C79">
-        <v>-70.07451350415818</v>
+        <v>-74.38310152137475</v>
       </c>
       <c r="D79">
-        <v>171.7743951848521</v>
+        <v>170.7599488389213</v>
       </c>
       <c r="E79">
-        <v>-29.36525843957449</v>
+        <v>-26.07111676828868</v>
       </c>
       <c r="F79">
-        <v>253.6489086890103</v>
+        <v>256.9430503602961</v>
       </c>
       <c r="G79">
         <v>11.8</v>
@@ -7765,28 +7765,28 @@
         <v>34.89375</v>
       </c>
       <c r="M79">
-        <v>22.82840178201092</v>
+        <v>23.12487453242665</v>
       </c>
       <c r="N79">
-        <v>12.06534821798908</v>
+        <v>11.76887546757335</v>
       </c>
       <c r="O79">
-        <v>1.761540839826405</v>
+        <v>1.718255818265709</v>
       </c>
       <c r="P79">
-        <v>10.30380737816267</v>
+        <v>10.05061964930764</v>
       </c>
       <c r="Q79">
-        <v>17.53380737816267</v>
+        <v>17.28061964930765</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1423886753657174</v>
+        <v>0.1466129669923018</v>
       </c>
       <c r="T79">
-        <v>2.230685343319108</v>
+        <v>2.32824404139265</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.528523561710602</v>
+        <v>1.508927105791236</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09220565273830639</v>
+        <v>0.1325170702844536</v>
       </c>
       <c r="C80">
-        <v>-74.38310152137475</v>
+        <v>-157.056949808955</v>
       </c>
       <c r="D80">
-        <v>170.7599488389213</v>
+        <v>91.380242222627</v>
       </c>
       <c r="E80">
-        <v>-26.07111676828868</v>
+        <v>-22.77697509700278</v>
       </c>
       <c r="F80">
-        <v>256.9430503602961</v>
+        <v>260.237192031582</v>
       </c>
       <c r="G80">
         <v>11.8</v>
@@ -7847,45 +7847,45 @@
         <v>34.89375</v>
       </c>
       <c r="M80">
-        <v>23.12487453242665</v>
+        <v>38.20281979023623</v>
       </c>
       <c r="N80">
-        <v>11.76887546757335</v>
+        <v>-3.309069790236236</v>
       </c>
       <c r="O80">
-        <v>1.718255818265709</v>
+        <v>-0.4831241893744905</v>
       </c>
       <c r="P80">
-        <v>10.05061964930764</v>
+        <v>-2.825945600861746</v>
       </c>
       <c r="Q80">
-        <v>17.28061964930765</v>
+        <v>4.404054399138254</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1466129669923018</v>
+        <v>0.1524303141768056</v>
       </c>
       <c r="T80">
-        <v>2.32824404139265</v>
+        <v>2.462593860896202</v>
       </c>
       <c r="U80">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.146</v>
+        <v>0.1333537034169932</v>
       </c>
       <c r="W80">
-        <v>0.07686</v>
+        <v>0.1272236763383854</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.508927105791236</v>
+        <v>0.9133815302533779</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1325170702844536</v>
+        <v>0.1335270702844536</v>
       </c>
       <c r="C81">
-        <v>-157.056949808955</v>
+        <v>-161.4031503754665</v>
       </c>
       <c r="D81">
-        <v>91.380242222627</v>
+        <v>90.32818332740131</v>
       </c>
       <c r="E81">
-        <v>-22.77697509700278</v>
+        <v>-19.48283342571693</v>
       </c>
       <c r="F81">
-        <v>260.237192031582</v>
+        <v>263.5313337028678</v>
       </c>
       <c r="G81">
         <v>11.8</v>
@@ -7929,37 +7929,37 @@
         <v>34.89375</v>
       </c>
       <c r="M81">
-        <v>38.20281979023623</v>
+        <v>38.686399787581</v>
       </c>
       <c r="N81">
-        <v>-3.309069790236236</v>
+        <v>-3.792649787580999</v>
       </c>
       <c r="O81">
-        <v>-0.4831241893744905</v>
+        <v>-0.5537268689868258</v>
       </c>
       <c r="P81">
-        <v>-2.825945600861746</v>
+        <v>-3.238922918594173</v>
       </c>
       <c r="Q81">
-        <v>4.404054399138254</v>
+        <v>3.991077081405828</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1524303141768056</v>
+        <v>0.1577618298856458</v>
       </c>
       <c r="T81">
-        <v>2.462593860896202</v>
+        <v>2.585723553941012</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1333537034169932</v>
+        <v>0.1316867821242807</v>
       </c>
       <c r="W81">
-        <v>0.1272236763383854</v>
+        <v>0.1274683803841556</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9133815302533779</v>
+        <v>0.9019642611252106</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1335270702844536</v>
+        <v>0.1345370702844536</v>
       </c>
       <c r="C82">
-        <v>-161.4031503754665</v>
+        <v>-165.7254019997656</v>
       </c>
       <c r="D82">
-        <v>90.32818332740131</v>
+        <v>89.30007337438811</v>
       </c>
       <c r="E82">
-        <v>-19.48283342571693</v>
+        <v>-16.18869175443109</v>
       </c>
       <c r="F82">
-        <v>263.5313337028678</v>
+        <v>266.8254753741537</v>
       </c>
       <c r="G82">
         <v>11.8</v>
@@ -8011,37 +8011,37 @@
         <v>34.89375</v>
       </c>
       <c r="M82">
-        <v>38.686399787581</v>
+        <v>39.16997978492576</v>
       </c>
       <c r="N82">
-        <v>-3.792649787580999</v>
+        <v>-4.276229784925761</v>
       </c>
       <c r="O82">
-        <v>-0.5537268689868258</v>
+        <v>-0.624329548599161</v>
       </c>
       <c r="P82">
-        <v>-3.238922918594173</v>
+        <v>-3.6519002363266</v>
       </c>
       <c r="Q82">
-        <v>3.991077081405828</v>
+        <v>3.578099763673401</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1577618298856458</v>
+        <v>0.1636545577743641</v>
       </c>
       <c r="T82">
-        <v>2.585723553941012</v>
+        <v>2.721814267306329</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1316867821242807</v>
+        <v>0.1300610193820057</v>
       </c>
       <c r="W82">
-        <v>0.1274683803841556</v>
+        <v>0.1277070423547216</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.9019642611252106</v>
+        <v>0.8908288998767512</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1345370702844536</v>
+        <v>0.1355470702844536</v>
       </c>
       <c r="C83">
-        <v>-165.7254019997656</v>
+        <v>-170.0245132352084</v>
       </c>
       <c r="D83">
-        <v>89.30007337438811</v>
+        <v>88.29510381023113</v>
       </c>
       <c r="E83">
-        <v>-16.18869175443109</v>
+        <v>-12.89455008314525</v>
       </c>
       <c r="F83">
-        <v>266.8254753741537</v>
+        <v>270.1196170454395</v>
       </c>
       <c r="G83">
         <v>11.8</v>
@@ -8093,37 +8093,37 @@
         <v>34.89375</v>
       </c>
       <c r="M83">
-        <v>39.16997978492576</v>
+        <v>39.65355978227052</v>
       </c>
       <c r="N83">
-        <v>-4.276229784925761</v>
+        <v>-4.759809782270523</v>
       </c>
       <c r="O83">
-        <v>-0.624329548599161</v>
+        <v>-0.6949322282114963</v>
       </c>
       <c r="P83">
-        <v>-3.6519002363266</v>
+        <v>-4.064877554059026</v>
       </c>
       <c r="Q83">
-        <v>3.578099763673401</v>
+        <v>3.165122445940974</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1636545577743641</v>
+        <v>0.1702020332062732</v>
       </c>
       <c r="T83">
-        <v>2.721814267306329</v>
+        <v>2.87302617104557</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1300610193820057</v>
+        <v>0.1284749093895422</v>
       </c>
       <c r="W83">
-        <v>0.1277070423547216</v>
+        <v>0.1279398833016152</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8908288998767512</v>
+        <v>0.8799651328050835</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1355470702844536</v>
+        <v>0.1365570702844537</v>
       </c>
       <c r="C84">
-        <v>-170.0245132352084</v>
+        <v>-174.3012566428529</v>
       </c>
       <c r="D84">
-        <v>88.29510381023113</v>
+        <v>87.31250207387244</v>
       </c>
       <c r="E84">
-        <v>-12.89455008314525</v>
+        <v>-9.600408411859405</v>
       </c>
       <c r="F84">
-        <v>270.1196170454395</v>
+        <v>273.4137587167253</v>
       </c>
       <c r="G84">
         <v>11.8</v>
@@ -8175,37 +8175,37 @@
         <v>34.89375</v>
       </c>
       <c r="M84">
-        <v>39.65355978227052</v>
+        <v>40.13713977961528</v>
       </c>
       <c r="N84">
-        <v>-4.759809782270523</v>
+        <v>-5.243389779615285</v>
       </c>
       <c r="O84">
-        <v>-0.6949322282114963</v>
+        <v>-0.7655349078238315</v>
       </c>
       <c r="P84">
-        <v>-4.064877554059026</v>
+        <v>-4.477854871791453</v>
       </c>
       <c r="Q84">
-        <v>3.165122445940974</v>
+        <v>2.752145128208547</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1702020332062732</v>
+        <v>0.1775197998654657</v>
       </c>
       <c r="T84">
-        <v>2.87302617104557</v>
+        <v>3.042027710518839</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1284749093895422</v>
+        <v>0.1269270189149694</v>
       </c>
       <c r="W84">
-        <v>0.1279398833016152</v>
+        <v>0.1281671136232825</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8799651328050835</v>
+        <v>0.8693631432532151</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1365570702844537</v>
+        <v>0.1375670702844536</v>
       </c>
       <c r="C85">
-        <v>-174.3012566428529</v>
+        <v>-178.5563707721377</v>
       </c>
       <c r="D85">
-        <v>87.31250207387244</v>
+        <v>86.35152961587353</v>
       </c>
       <c r="E85">
-        <v>-9.600408411859405</v>
+        <v>-6.306266740573562</v>
       </c>
       <c r="F85">
-        <v>273.4137587167253</v>
+        <v>276.7079003880112</v>
       </c>
       <c r="G85">
         <v>11.8</v>
@@ -8257,37 +8257,37 @@
         <v>34.89375</v>
       </c>
       <c r="M85">
-        <v>40.13713977961528</v>
+        <v>40.62071977696004</v>
       </c>
       <c r="N85">
-        <v>-5.243389779615285</v>
+        <v>-5.726969776960047</v>
       </c>
       <c r="O85">
-        <v>-0.7655349078238315</v>
+        <v>-0.8361375874361668</v>
       </c>
       <c r="P85">
-        <v>-4.477854871791453</v>
+        <v>-4.89083218952388</v>
       </c>
       <c r="Q85">
-        <v>2.752145128208547</v>
+        <v>2.339167810476121</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1775197998654657</v>
+        <v>0.1857522873570573</v>
       </c>
       <c r="T85">
-        <v>3.042027710518839</v>
+        <v>3.232154442426267</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1269270189149694</v>
+        <v>0.1254159829755055</v>
       </c>
       <c r="W85">
-        <v>0.1281671136232825</v>
+        <v>0.1283889336991958</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8693631432532151</v>
+        <v>0.8590135820240101</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1375670702844536</v>
+        <v>0.1385770702844537</v>
       </c>
       <c r="C86">
-        <v>-178.5563707721377</v>
+        <v>-182.7905620121869</v>
       </c>
       <c r="D86">
-        <v>86.35152961587353</v>
+        <v>85.41148004711012</v>
       </c>
       <c r="E86">
-        <v>-6.306266740573562</v>
+        <v>-3.01212506928772</v>
       </c>
       <c r="F86">
-        <v>276.7079003880112</v>
+        <v>280.002042059297</v>
       </c>
       <c r="G86">
         <v>11.8</v>
@@ -8339,37 +8339,37 @@
         <v>34.89375</v>
       </c>
       <c r="M86">
-        <v>40.62071977696004</v>
+        <v>41.10429977430481</v>
       </c>
       <c r="N86">
-        <v>-5.726969776960047</v>
+        <v>-6.210549774304809</v>
       </c>
       <c r="O86">
-        <v>-0.8361375874361668</v>
+        <v>-0.9067402670485021</v>
       </c>
       <c r="P86">
-        <v>-4.89083218952388</v>
+        <v>-5.303809507256307</v>
       </c>
       <c r="Q86">
-        <v>2.339167810476121</v>
+        <v>1.926190492743693</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1857522873570573</v>
+        <v>0.1950824398475278</v>
       </c>
       <c r="T86">
-        <v>3.232154442426265</v>
+        <v>3.447631405254683</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1254159829755055</v>
+        <v>0.1239405008228525</v>
       </c>
       <c r="W86">
-        <v>0.1283889336991958</v>
+        <v>0.1286055344792053</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8590135820240101</v>
+        <v>0.8489075398825512</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1385770702844537</v>
+        <v>0.1395870702844536</v>
       </c>
       <c r="C87">
-        <v>-182.7905620121869</v>
+        <v>-187.0045063234949</v>
       </c>
       <c r="D87">
-        <v>85.41148004711012</v>
+        <v>84.49167740708799</v>
       </c>
       <c r="E87">
-        <v>-3.01212506928772</v>
+        <v>0.282016601998123</v>
       </c>
       <c r="F87">
-        <v>280.002042059297</v>
+        <v>283.2961837305829</v>
       </c>
       <c r="G87">
         <v>11.8</v>
@@ -8421,37 +8421,37 @@
         <v>34.89375</v>
       </c>
       <c r="M87">
-        <v>41.10429977430481</v>
+        <v>41.58787977164957</v>
       </c>
       <c r="N87">
-        <v>-6.210549774304809</v>
+        <v>-6.694129771649571</v>
       </c>
       <c r="O87">
-        <v>-0.9067402670485021</v>
+        <v>-0.9773429466608373</v>
       </c>
       <c r="P87">
-        <v>-5.303809507256307</v>
+        <v>-5.716786824988734</v>
       </c>
       <c r="Q87">
-        <v>1.926190492743693</v>
+        <v>1.513213175011266</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1950824398475278</v>
+        <v>0.2057454712652083</v>
       </c>
       <c r="T87">
-        <v>3.447631405254683</v>
+        <v>3.693890791344303</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1239405008228525</v>
+        <v>0.1224993322086333</v>
       </c>
       <c r="W87">
-        <v>0.1286055344792053</v>
+        <v>0.1288170980317726</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8489075398825512</v>
+        <v>0.8390365219769401</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1395870702844536</v>
+        <v>0.1405970702844536</v>
       </c>
       <c r="C88">
-        <v>-187.0045063234949</v>
+        <v>-191.1988508589103</v>
       </c>
       <c r="D88">
-        <v>84.49167740708799</v>
+        <v>83.59147454295839</v>
       </c>
       <c r="E88">
-        <v>0.282016601998123</v>
+        <v>3.576158273283966</v>
       </c>
       <c r="F88">
-        <v>283.2961837305829</v>
+        <v>286.5903254018687</v>
       </c>
       <c r="G88">
         <v>11.8</v>
@@ -8503,37 +8503,37 @@
         <v>34.89375</v>
       </c>
       <c r="M88">
-        <v>41.58787977164957</v>
+        <v>42.07145976899433</v>
       </c>
       <c r="N88">
-        <v>-6.694129771649571</v>
+        <v>-7.177709768994333</v>
       </c>
       <c r="O88">
-        <v>-0.9773429466608373</v>
+        <v>-1.047945626273173</v>
       </c>
       <c r="P88">
-        <v>-5.716786824988734</v>
+        <v>-6.129764142721161</v>
       </c>
       <c r="Q88">
-        <v>1.513213175011266</v>
+        <v>1.10023585727884</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2057454712652083</v>
+        <v>0.2180489690548397</v>
       </c>
       <c r="T88">
-        <v>3.693890791344303</v>
+        <v>3.978036236832326</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1224993322086333</v>
+        <v>0.1210912939073846</v>
       </c>
       <c r="W88">
-        <v>0.1288170980317726</v>
+        <v>0.129023798054396</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8390365219769401</v>
+        <v>0.8293924240231823</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1405970702844536</v>
+        <v>0.1416070702844537</v>
       </c>
       <c r="C89">
-        <v>-191.1988508589103</v>
+        <v>-195.3742154820902</v>
       </c>
       <c r="D89">
-        <v>83.59147454295839</v>
+        <v>82.71025159106432</v>
       </c>
       <c r="E89">
-        <v>3.576158273283966</v>
+        <v>6.870299944569808</v>
       </c>
       <c r="F89">
-        <v>286.5903254018687</v>
+        <v>289.8844670731546</v>
       </c>
       <c r="G89">
         <v>11.8</v>
@@ -8585,37 +8585,37 @@
         <v>34.89375</v>
       </c>
       <c r="M89">
-        <v>42.07145976899433</v>
+        <v>42.55503976633909</v>
       </c>
       <c r="N89">
-        <v>-7.177709768994333</v>
+        <v>-7.661289766339095</v>
       </c>
       <c r="O89">
-        <v>-1.047945626273173</v>
+        <v>-1.118548305885508</v>
       </c>
       <c r="P89">
-        <v>-6.129764142721161</v>
+        <v>-6.542741460453588</v>
       </c>
       <c r="Q89">
-        <v>1.10023585727884</v>
+        <v>0.6872585395464128</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2180489690548397</v>
+        <v>0.2324030498094097</v>
       </c>
       <c r="T89">
-        <v>3.978036236832326</v>
+        <v>4.309539256568354</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1210912939073846</v>
+        <v>0.1197152564766189</v>
       </c>
       <c r="W89">
-        <v>0.129023798054396</v>
+        <v>0.1292258003492324</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8293924240231823</v>
+        <v>0.8199675101138278</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1416070702844537</v>
+        <v>0.1426170702844536</v>
       </c>
       <c r="C90">
-        <v>-195.3742154820902</v>
+        <v>-199.5311941909102</v>
       </c>
       <c r="D90">
-        <v>82.71025159106432</v>
+        <v>81.84741455353017</v>
       </c>
       <c r="E90">
-        <v>6.870299944569808</v>
+        <v>10.16444161585565</v>
       </c>
       <c r="F90">
-        <v>289.8844670731546</v>
+        <v>293.1786087444404</v>
       </c>
       <c r="G90">
         <v>11.8</v>
@@ -8667,37 +8667,37 @@
         <v>34.89375</v>
       </c>
       <c r="M90">
-        <v>42.55503976633909</v>
+        <v>43.03861976368385</v>
       </c>
       <c r="N90">
-        <v>-7.661289766339095</v>
+        <v>-8.144869763683857</v>
       </c>
       <c r="O90">
-        <v>-1.118548305885508</v>
+        <v>-1.189150985497843</v>
       </c>
       <c r="P90">
-        <v>-6.542741460453588</v>
+        <v>-6.955718778186014</v>
       </c>
       <c r="Q90">
-        <v>0.6872585395464128</v>
+        <v>0.2742812218139861</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2324030498094097</v>
+        <v>0.249366963428447</v>
       </c>
       <c r="T90">
-        <v>4.309539256568354</v>
+        <v>4.701315552620023</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1197152564766189</v>
+        <v>0.1183701412353085</v>
       </c>
       <c r="W90">
-        <v>0.1292258003492324</v>
+        <v>0.1294232632666567</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8199675101138278</v>
+        <v>0.8107543920226613</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1426170702844536</v>
+        <v>0.1436270702844536</v>
       </c>
       <c r="C91">
-        <v>-199.5311941909102</v>
+        <v>-203.6703564527003</v>
       </c>
       <c r="D91">
-        <v>81.84741455353017</v>
+        <v>81.00239396302598</v>
       </c>
       <c r="E91">
-        <v>10.16444161585565</v>
+        <v>13.45858328714149</v>
       </c>
       <c r="F91">
-        <v>293.1786087444404</v>
+        <v>296.4727504157262</v>
       </c>
       <c r="G91">
         <v>11.8</v>
@@ -8749,37 +8749,37 @@
         <v>34.89375</v>
       </c>
       <c r="M91">
-        <v>43.03861976368385</v>
+        <v>43.52219976102862</v>
       </c>
       <c r="N91">
-        <v>-8.144869763683857</v>
+        <v>-8.628449761028619</v>
       </c>
       <c r="O91">
-        <v>-1.189150985497843</v>
+        <v>-1.259753665110178</v>
       </c>
       <c r="P91">
-        <v>-6.955718778186014</v>
+        <v>-7.368696095918441</v>
       </c>
       <c r="Q91">
-        <v>0.2742812218139861</v>
+        <v>-0.1386960959184407</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.249366963428447</v>
+        <v>0.2697236597712916</v>
       </c>
       <c r="T91">
-        <v>4.701315552620023</v>
+        <v>5.171447107882025</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1183701412353085</v>
+        <v>0.1170549174438051</v>
       </c>
       <c r="W91">
-        <v>0.1294232632666567</v>
+        <v>0.1296163381192494</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8107543920226613</v>
+        <v>0.8017460098890762</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1436270702844536</v>
+        <v>0.1944861723693612</v>
       </c>
       <c r="C92">
-        <v>-203.6703564527003</v>
+        <v>-234.6719100375391</v>
       </c>
       <c r="D92">
-        <v>81.00239396302598</v>
+        <v>53.29498204947295</v>
       </c>
       <c r="E92">
-        <v>13.45858328714149</v>
+        <v>16.75272495842734</v>
       </c>
       <c r="F92">
-        <v>296.4727504157262</v>
+        <v>299.7668920870121</v>
       </c>
       <c r="G92">
         <v>11.8</v>
@@ -8831,45 +8831,45 @@
         <v>34.89375</v>
       </c>
       <c r="M92">
-        <v>43.52219976102862</v>
+        <v>60.19319193107203</v>
       </c>
       <c r="N92">
-        <v>-8.628449761028619</v>
+        <v>-25.29944193107203</v>
       </c>
       <c r="O92">
-        <v>-1.259753665110178</v>
+        <v>-3.693718521936516</v>
       </c>
       <c r="P92">
-        <v>-7.368696095918441</v>
+        <v>-21.60572340913551</v>
       </c>
       <c r="Q92">
-        <v>-0.1386960959184407</v>
+        <v>-14.37572340913551</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2697236597712916</v>
+        <v>0.3024829784670751</v>
       </c>
       <c r="T92">
-        <v>5.171447107882025</v>
+        <v>5.928013359516746</v>
       </c>
       <c r="U92">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1170549174438051</v>
+        <v>0.08463560971868314</v>
       </c>
       <c r="W92">
-        <v>0.1296163381192494</v>
+        <v>0.1838051695684884</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.8017460098890762</v>
+        <v>0.5796959569772818</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1944861723693612</v>
+        <v>0.1960361723693612</v>
       </c>
       <c r="C93">
-        <v>-234.6719100375391</v>
+        <v>-238.5159007955922</v>
       </c>
       <c r="D93">
-        <v>53.29498204947295</v>
+        <v>52.74513296270578</v>
       </c>
       <c r="E93">
-        <v>16.75272495842734</v>
+        <v>20.04686662971324</v>
       </c>
       <c r="F93">
-        <v>299.7668920870121</v>
+        <v>303.061033758298</v>
       </c>
       <c r="G93">
         <v>11.8</v>
@@ -8913,37 +8913,37 @@
         <v>34.89375</v>
       </c>
       <c r="M93">
-        <v>60.19319193107203</v>
+        <v>60.85465557866624</v>
       </c>
       <c r="N93">
-        <v>-25.29944193107203</v>
+        <v>-25.96090557866624</v>
       </c>
       <c r="O93">
-        <v>-3.693718521936516</v>
+        <v>-3.790292214485271</v>
       </c>
       <c r="P93">
-        <v>-21.60572340913551</v>
+        <v>-22.17061336418097</v>
       </c>
       <c r="Q93">
-        <v>-14.37572340913551</v>
+        <v>-14.94061336418097</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3024829784670751</v>
+        <v>0.3345683507754596</v>
       </c>
       <c r="T93">
-        <v>5.928013359516746</v>
+        <v>6.669015029456342</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08463560971868314</v>
+        <v>0.08371565743913222</v>
       </c>
       <c r="W93">
-        <v>0.1838051695684884</v>
+        <v>0.1839898959862223</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5796959569772818</v>
+        <v>0.573394913966659</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1960361723693612</v>
+        <v>0.1975861723693613</v>
       </c>
       <c r="C94">
-        <v>-238.5159007955922</v>
+        <v>-242.3486617285407</v>
       </c>
       <c r="D94">
-        <v>52.74513296270578</v>
+        <v>52.20651370104307</v>
       </c>
       <c r="E94">
-        <v>20.04686662971324</v>
+        <v>23.34100830099908</v>
       </c>
       <c r="F94">
-        <v>303.061033758298</v>
+        <v>306.3551754295838</v>
       </c>
       <c r="G94">
         <v>11.8</v>
@@ -8995,37 +8995,37 @@
         <v>34.89375</v>
       </c>
       <c r="M94">
-        <v>60.85465557866624</v>
+        <v>61.51611922626044</v>
       </c>
       <c r="N94">
-        <v>-25.96090557866624</v>
+        <v>-26.62236922626044</v>
       </c>
       <c r="O94">
-        <v>-3.790292214485271</v>
+        <v>-3.886865907034024</v>
       </c>
       <c r="P94">
-        <v>-22.17061336418097</v>
+        <v>-22.73550331922641</v>
       </c>
       <c r="Q94">
-        <v>-14.94061336418097</v>
+        <v>-15.50550331922641</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3345683507754596</v>
+        <v>0.375820972314811</v>
       </c>
       <c r="T94">
-        <v>6.669015029456342</v>
+        <v>7.621731462235821</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08371565743913222</v>
+        <v>0.08281548907957165</v>
       </c>
       <c r="W94">
-        <v>0.1839898959862223</v>
+        <v>0.184170649792822</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.573394913966659</v>
+        <v>0.5672293772573402</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1975861723693613</v>
+        <v>0.1991361723693612</v>
       </c>
       <c r="C95">
-        <v>-242.3486617285407</v>
+        <v>-246.170533386732</v>
       </c>
       <c r="D95">
-        <v>52.20651370104307</v>
+        <v>51.67878371413763</v>
       </c>
       <c r="E95">
-        <v>23.34100830099908</v>
+        <v>26.63514997228492</v>
       </c>
       <c r="F95">
-        <v>306.3551754295838</v>
+        <v>309.6493171008697</v>
       </c>
       <c r="G95">
         <v>11.8</v>
@@ -9077,37 +9077,37 @@
         <v>34.89375</v>
       </c>
       <c r="M95">
-        <v>61.51611922626044</v>
+        <v>62.17758287385463</v>
       </c>
       <c r="N95">
-        <v>-26.62236922626044</v>
+        <v>-27.28383287385464</v>
       </c>
       <c r="O95">
-        <v>-3.886865907034024</v>
+        <v>-3.983439599582776</v>
       </c>
       <c r="P95">
-        <v>-22.73550331922641</v>
+        <v>-23.30039327427186</v>
       </c>
       <c r="Q95">
-        <v>-15.50550331922641</v>
+        <v>-16.07039327427186</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.375820972314811</v>
+        <v>0.4308244677006129</v>
       </c>
       <c r="T95">
-        <v>7.621731462235821</v>
+        <v>8.892020039275126</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08281548907957165</v>
+        <v>0.08193447323829961</v>
       </c>
       <c r="W95">
-        <v>0.184170649792822</v>
+        <v>0.1843475577737494</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5672293772573402</v>
+        <v>0.5611950221801345</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1991361723693612</v>
+        <v>0.2006861723693613</v>
       </c>
       <c r="C96">
-        <v>-246.170533386732</v>
+        <v>-249.9818426884884</v>
       </c>
       <c r="D96">
-        <v>51.67878371413763</v>
+        <v>51.16161608366708</v>
       </c>
       <c r="E96">
-        <v>26.63514997228492</v>
+        <v>29.92929164357076</v>
       </c>
       <c r="F96">
-        <v>309.6493171008697</v>
+        <v>312.9434587721555</v>
       </c>
       <c r="G96">
         <v>11.8</v>
@@ -9159,37 +9159,37 @@
         <v>34.89375</v>
       </c>
       <c r="M96">
-        <v>62.17758287385463</v>
+        <v>62.83904652144883</v>
       </c>
       <c r="N96">
-        <v>-27.28383287385464</v>
+        <v>-27.94529652144883</v>
       </c>
       <c r="O96">
-        <v>-3.983439599582776</v>
+        <v>-4.080013292131529</v>
       </c>
       <c r="P96">
-        <v>-23.30039327427186</v>
+        <v>-23.8652832293173</v>
       </c>
       <c r="Q96">
-        <v>-16.07039327427186</v>
+        <v>-16.6352832293173</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4308244677006129</v>
+        <v>0.5078293612407357</v>
       </c>
       <c r="T96">
-        <v>8.892020039275126</v>
+        <v>10.67042404713016</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.08193447323829961</v>
+        <v>0.0810720050989491</v>
       </c>
       <c r="W96">
-        <v>0.1843475577737494</v>
+        <v>0.184520741376131</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5611950221801345</v>
+        <v>0.5552877061571857</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2006861723693613</v>
+        <v>0.2022361723693613</v>
       </c>
       <c r="C97">
-        <v>-249.9818426884884</v>
+        <v>-253.7829035954511</v>
       </c>
       <c r="D97">
-        <v>51.16161608366708</v>
+        <v>50.65469684799027</v>
       </c>
       <c r="E97">
-        <v>29.92929164357076</v>
+        <v>33.22343331485661</v>
       </c>
       <c r="F97">
-        <v>312.9434587721555</v>
+        <v>316.2376004434414</v>
       </c>
       <c r="G97">
         <v>11.8</v>
@@ -9241,37 +9241,37 @@
         <v>34.89375</v>
       </c>
       <c r="M97">
-        <v>62.83904652144883</v>
+        <v>63.50051016904303</v>
       </c>
       <c r="N97">
-        <v>-27.94529652144883</v>
+        <v>-28.60676016904303</v>
       </c>
       <c r="O97">
-        <v>-4.080013292131529</v>
+        <v>-4.176586984680282</v>
       </c>
       <c r="P97">
-        <v>-23.8652832293173</v>
+        <v>-24.43017318436275</v>
       </c>
       <c r="Q97">
-        <v>-16.6352832293173</v>
+        <v>-17.20017318436275</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5078293612407357</v>
+        <v>0.6233367015509198</v>
       </c>
       <c r="T97">
-        <v>10.67042404713016</v>
+        <v>13.3380300589127</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.0810720050989491</v>
+        <v>0.08022750504583505</v>
       </c>
       <c r="W97">
-        <v>0.184520741376131</v>
+        <v>0.1846903169867963</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5552877061571857</v>
+        <v>0.5495034592180483</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2022361723693612</v>
+        <v>0.2037861723693612</v>
       </c>
       <c r="C98">
-        <v>-253.782903595451</v>
+        <v>-257.5740177481692</v>
       </c>
       <c r="D98">
-        <v>50.65469684799027</v>
+        <v>50.15772436655801</v>
       </c>
       <c r="E98">
-        <v>33.22343331485655</v>
+        <v>36.51757498614245</v>
       </c>
       <c r="F98">
-        <v>316.2376004434413</v>
+        <v>319.5317421147272</v>
       </c>
       <c r="G98">
         <v>11.8</v>
@@ -9323,37 +9323,37 @@
         <v>34.89375</v>
       </c>
       <c r="M98">
-        <v>63.50051016904301</v>
+        <v>64.16197381663723</v>
       </c>
       <c r="N98">
-        <v>-28.60676016904301</v>
+        <v>-29.26822381663723</v>
       </c>
       <c r="O98">
-        <v>-4.17658698468028</v>
+        <v>-4.273160677229035</v>
       </c>
       <c r="P98">
-        <v>-24.43017318436273</v>
+        <v>-24.9950631394082</v>
       </c>
       <c r="Q98">
-        <v>-17.20017318436273</v>
+        <v>-17.76506313940819</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6233367015509182</v>
+        <v>0.8158489354012244</v>
       </c>
       <c r="T98">
-        <v>13.33803005891266</v>
+        <v>17.78404007855022</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08022750504583506</v>
+        <v>0.07940041736495015</v>
       </c>
       <c r="W98">
-        <v>0.1846903169867963</v>
+        <v>0.184856396193118</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5495034592180484</v>
+        <v>0.5438384751023984</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2037861723693612</v>
+        <v>0.2053361723693612</v>
       </c>
       <c r="C99">
-        <v>-257.5740177481692</v>
+        <v>-261.3554750646378</v>
       </c>
       <c r="D99">
-        <v>50.15772436655801</v>
+        <v>49.67040872137524</v>
       </c>
       <c r="E99">
-        <v>36.51757498614245</v>
+        <v>39.81171665742829</v>
       </c>
       <c r="F99">
-        <v>319.5317421147272</v>
+        <v>322.825883786013</v>
       </c>
       <c r="G99">
         <v>11.8</v>
@@ -9405,37 +9405,37 @@
         <v>34.89375</v>
       </c>
       <c r="M99">
-        <v>64.16197381663723</v>
+        <v>64.82343746423142</v>
       </c>
       <c r="N99">
-        <v>-29.26822381663723</v>
+        <v>-29.92968746423142</v>
       </c>
       <c r="O99">
-        <v>-4.273160677229035</v>
+        <v>-4.369734369777787</v>
       </c>
       <c r="P99">
-        <v>-24.9950631394082</v>
+        <v>-25.55995309445363</v>
       </c>
       <c r="Q99">
-        <v>-17.76506313940819</v>
+        <v>-18.32995309445363</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8158489354012244</v>
+        <v>1.200873403101837</v>
       </c>
       <c r="T99">
-        <v>17.78404007855022</v>
+        <v>26.67606011782533</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07940041736495015</v>
+        <v>0.07859020902449147</v>
       </c>
       <c r="W99">
-        <v>0.184856396193118</v>
+        <v>0.1850190860278821</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5438384751023984</v>
+        <v>0.5382891029074759</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2053361723693612</v>
+        <v>0.2068861723693612</v>
       </c>
       <c r="C100">
-        <v>-261.3554750646378</v>
+        <v>-265.1275543042805</v>
       </c>
       <c r="D100">
-        <v>49.67040872137524</v>
+        <v>49.19247115301835</v>
       </c>
       <c r="E100">
-        <v>39.81171665742829</v>
+        <v>43.10585832871413</v>
       </c>
       <c r="F100">
-        <v>322.825883786013</v>
+        <v>326.1200254572989</v>
       </c>
       <c r="G100">
         <v>11.8</v>
@@ -9487,37 +9487,37 @@
         <v>34.89375</v>
       </c>
       <c r="M100">
-        <v>64.82343746423142</v>
+        <v>65.48490111182562</v>
       </c>
       <c r="N100">
-        <v>-29.92968746423142</v>
+        <v>-30.59115111182562</v>
       </c>
       <c r="O100">
-        <v>-4.369734369777787</v>
+        <v>-4.466308062326541</v>
       </c>
       <c r="P100">
-        <v>-25.55995309445363</v>
+        <v>-26.12484304949908</v>
       </c>
       <c r="Q100">
-        <v>-18.32995309445363</v>
+        <v>-18.89484304949908</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.200873403101837</v>
+        <v>2.355946806203673</v>
       </c>
       <c r="T100">
-        <v>26.67606011782533</v>
+        <v>53.35212023565065</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.07859020902449147</v>
+        <v>0.0777963685292946</v>
       </c>
       <c r="W100">
-        <v>0.1850190860278821</v>
+        <v>0.1851784891993176</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5382891029074759</v>
+        <v>0.5328518392417438</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2068861723693612</v>
-      </c>
-      <c r="C101">
-        <v>-265.1275543042805</v>
-      </c>
-      <c r="D101">
-        <v>49.19247115301835</v>
-      </c>
-      <c r="E101">
-        <v>43.10585832871413</v>
-      </c>
-      <c r="F101">
-        <v>326.1200254572989</v>
-      </c>
-      <c r="G101">
-        <v>11.8</v>
-      </c>
-      <c r="H101">
-        <v>46.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>42.12374999999999</v>
-      </c>
-      <c r="K101">
-        <v>7.23</v>
-      </c>
-      <c r="L101">
-        <v>34.89375</v>
-      </c>
-      <c r="M101">
-        <v>65.48490111182562</v>
-      </c>
-      <c r="N101">
-        <v>-30.59115111182562</v>
-      </c>
-      <c r="O101">
-        <v>-4.466308062326541</v>
-      </c>
-      <c r="P101">
-        <v>-26.12484304949908</v>
-      </c>
-      <c r="Q101">
-        <v>-18.89484304949908</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.355946806203673</v>
-      </c>
-      <c r="T101">
-        <v>53.35212023565065</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.0777963685292946</v>
-      </c>
-      <c r="W101">
-        <v>0.1851784891993176</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5328518392417438</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
